--- a/DOC/EM&REM/(분석,방안) NexacroK-상대단위(em,rem) 확장 지원.xlsx
+++ b/DOC/EM&REM/(분석,방안) NexacroK-상대단위(em,rem) 확장 지원.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobesoft\Desktop\em,rem\k\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_prj\REQM\DOC\EM&amp;REM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -212,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="781">
   <si>
     <t>문서 이력 정보(Revision History)</t>
   </si>
@@ -2040,9 +2040,6 @@
     <t>A·B·C</t>
   </si>
   <si>
-    <t>min-width</t>
-  </si>
-  <si>
     <t>10rem</t>
   </si>
   <si>
@@ -2079,9 +2076,6 @@
     <t xml:space="preserve">  ─ Padding ──────────</t>
   </si>
   <si>
-    <t>1em 2rem</t>
-  </si>
-  <si>
     <t>상하=1em(self), 좌우=2rem(MainFrame) 환산</t>
   </si>
   <si>
@@ -2151,9 +2145,6 @@
     <t>단어 간격 em 기준 적용</t>
   </si>
   <si>
-    <t>line-spacing</t>
-  </si>
-  <si>
     <t>줄 간격 em 기준 적용, 상속 동작 확인</t>
   </si>
   <si>
@@ -2182,9 +2173,6 @@
   </si>
   <si>
     <t>offset-x/y/blur em·rem 환산 후 DOM box-shadow 적용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ─ Gap / Layout ─────</t>
   </si>
   <si>
     <t>1rem</t>
@@ -2865,6 +2853,34 @@
   </si>
   <si>
     <t>em/rem 문자열을 JS에서 직접 px 정수로 환산, 레이아웃 계산에 사용</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>min-width</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>border</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ─ Gap / Layout ─────</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>1em 2rem</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>2rem</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>wordSpacing</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>line-spacing</t>
     <phoneticPr fontId="37" type="noConversion"/>
   </si>
 </sst>
@@ -4973,7 +4989,7 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5554,6 +5570,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5568,11 +5589,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5618,16 +5634,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5641,47 +5657,53 @@
     <xf numFmtId="0" fontId="50" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5692,14 +5714,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="266">
@@ -6835,7 +6857,7 @@
       <c r="A13" s="174"/>
       <c r="B13" s="178"/>
       <c r="C13" s="196" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="D13" s="197"/>
       <c r="E13" s="197"/>
@@ -6863,7 +6885,7 @@
       <c r="A15" s="174"/>
       <c r="B15" s="178"/>
       <c r="C15" s="198" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="D15" s="198"/>
       <c r="E15" s="198"/>
@@ -7138,7 +7160,7 @@
       <c r="A36" s="174"/>
       <c r="B36" s="178"/>
       <c r="C36" s="199" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D36" s="199"/>
       <c r="E36" s="199"/>
@@ -7251,20 +7273,20 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1"/>
     <row r="2" spans="2:4" ht="21.95" customHeight="1">
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="253" t="s">
         <v>397</v>
       </c>
       <c r="C2" s="244"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1"/>
     <row r="4" spans="2:4" ht="18" customHeight="1">
-      <c r="B4" s="250" t="s">
+      <c r="B4" s="247" t="s">
         <v>398</v>
       </c>
       <c r="C4" s="244"/>
     </row>
     <row r="5" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B5" s="247" t="s">
+      <c r="B5" s="250" t="s">
         <v>399</v>
       </c>
       <c r="C5" s="244"/>
@@ -7292,7 +7314,7 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B13" s="247" t="s">
+      <c r="B13" s="250" t="s">
         <v>404</v>
       </c>
       <c r="C13" s="244"/>
@@ -7304,7 +7326,7 @@
       <c r="C14" s="244"/>
     </row>
     <row r="15" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B15" s="247" t="s">
+      <c r="B15" s="250" t="s">
         <v>406</v>
       </c>
       <c r="C15" s="244"/>
@@ -7334,44 +7356,44 @@
       <c r="C19" s="244"/>
     </row>
     <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="253" t="s">
+      <c r="B20" s="252" t="s">
         <v>411</v>
       </c>
       <c r="C20" s="244"/>
     </row>
     <row r="21" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B21" s="248" t="s">
+      <c r="B21" s="251" t="s">
         <v>412</v>
       </c>
       <c r="C21" s="244"/>
     </row>
     <row r="22" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B22" s="248" t="s">
+      <c r="B22" s="251" t="s">
         <v>413</v>
       </c>
       <c r="C22" s="244"/>
     </row>
     <row r="23" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B23" s="248" t="s">
+      <c r="B23" s="251" t="s">
         <v>414</v>
       </c>
       <c r="C23" s="244"/>
     </row>
     <row r="24" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B24" s="248" t="s">
+      <c r="B24" s="251" t="s">
         <v>415</v>
       </c>
       <c r="C24" s="244"/>
     </row>
     <row r="25" spans="2:3" ht="6" customHeight="1"/>
     <row r="26" spans="2:3" ht="18" customHeight="1">
-      <c r="B26" s="250" t="s">
+      <c r="B26" s="247" t="s">
         <v>416</v>
       </c>
       <c r="C26" s="244"/>
     </row>
     <row r="27" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B27" s="247" t="s">
+      <c r="B27" s="250" t="s">
         <v>399</v>
       </c>
       <c r="C27" s="244"/>
@@ -7440,7 +7462,7 @@
       <c r="B46" s="159"/>
     </row>
     <row r="47" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B47" s="247" t="s">
+      <c r="B47" s="250" t="s">
         <v>419</v>
       </c>
       <c r="C47" s="244"/>
@@ -7458,7 +7480,7 @@
       <c r="C49" s="244"/>
     </row>
     <row r="50" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B50" s="247" t="s">
+      <c r="B50" s="250" t="s">
         <v>406</v>
       </c>
       <c r="C50" s="244"/>
@@ -7477,13 +7499,13 @@
     </row>
     <row r="53" spans="2:3" ht="6" customHeight="1"/>
     <row r="54" spans="2:3" ht="18" customHeight="1">
-      <c r="B54" s="250" t="s">
+      <c r="B54" s="247" t="s">
         <v>424</v>
       </c>
       <c r="C54" s="244"/>
     </row>
     <row r="55" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B55" s="247" t="s">
+      <c r="B55" s="250" t="s">
         <v>425</v>
       </c>
       <c r="C55" s="244"/>
@@ -7495,7 +7517,7 @@
       <c r="C56" s="244"/>
     </row>
     <row r="57" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B57" s="252" t="s">
+      <c r="B57" s="248" t="s">
         <v>427</v>
       </c>
       <c r="C57" s="244"/>
@@ -7504,7 +7526,7 @@
       <c r="B58" s="161"/>
     </row>
     <row r="59" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B59" s="247" t="s">
+      <c r="B59" s="250" t="s">
         <v>428</v>
       </c>
       <c r="C59" s="244"/>
@@ -7582,7 +7604,7 @@
       <c r="B80" s="159"/>
     </row>
     <row r="81" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B81" s="247" t="s">
+      <c r="B81" s="250" t="s">
         <v>404</v>
       </c>
       <c r="C81" s="244"/>
@@ -7594,7 +7616,7 @@
       <c r="C82" s="244"/>
     </row>
     <row r="83" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B83" s="247" t="s">
+      <c r="B83" s="250" t="s">
         <v>406</v>
       </c>
       <c r="C83" s="244"/>
@@ -7614,7 +7636,7 @@
     <row r="86" spans="2:3" ht="6" customHeight="1"/>
     <row r="87" spans="2:3" ht="6" customHeight="1"/>
     <row r="88" spans="2:3" ht="18" customHeight="1">
-      <c r="B88" s="250" t="s">
+      <c r="B88" s="247" t="s">
         <v>435</v>
       </c>
       <c r="C88" s="244"/>
@@ -7663,6 +7685,30 @@
     <row r="95" spans="2:3" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B88:C88"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B82:C82"/>
@@ -7679,30 +7725,6 @@
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B59:C59"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7725,7 +7747,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="6" customHeight="1"/>
     <row r="2" spans="2:5" ht="24" customHeight="1">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="258" t="s">
         <v>440</v>
       </c>
       <c r="C2" s="244"/>
@@ -7734,7 +7756,7 @@
     </row>
     <row r="3" spans="2:5" ht="6" customHeight="1"/>
     <row r="4" spans="2:5" ht="18" customHeight="1">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="254" t="s">
         <v>441</v>
       </c>
       <c r="C4" s="244"/>
@@ -7906,7 +7928,7 @@
     </row>
     <row r="18" spans="2:5" ht="6" customHeight="1"/>
     <row r="19" spans="2:5" ht="18" customHeight="1">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="254" t="s">
         <v>474</v>
       </c>
       <c r="C19" s="244"/>
@@ -7914,7 +7936,7 @@
       <c r="E19" s="244"/>
     </row>
     <row r="20" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B20" s="259" t="s">
+      <c r="B20" s="255" t="s">
         <v>475</v>
       </c>
       <c r="C20" s="244"/>
@@ -7922,7 +7944,7 @@
       <c r="E20" s="244"/>
     </row>
     <row r="21" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B21" s="255" t="s">
+      <c r="B21" s="259" t="s">
         <v>476</v>
       </c>
       <c r="C21" s="244"/>
@@ -7930,7 +7952,7 @@
       <c r="E21" s="244"/>
     </row>
     <row r="22" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B22" s="254" t="s">
+      <c r="B22" s="256" t="s">
         <v>477</v>
       </c>
       <c r="C22" s="244"/>
@@ -7938,7 +7960,7 @@
       <c r="E22" s="244"/>
     </row>
     <row r="23" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B23" s="254" t="s">
+      <c r="B23" s="256" t="s">
         <v>478</v>
       </c>
       <c r="C23" s="244"/>
@@ -7946,7 +7968,7 @@
       <c r="E23" s="244"/>
     </row>
     <row r="24" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B24" s="254" t="s">
+      <c r="B24" s="256" t="s">
         <v>479</v>
       </c>
       <c r="C24" s="244"/>
@@ -7954,7 +7976,7 @@
       <c r="E24" s="244"/>
     </row>
     <row r="25" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="256" t="s">
         <v>480</v>
       </c>
       <c r="C25" s="244"/>
@@ -7962,7 +7984,7 @@
       <c r="E25" s="244"/>
     </row>
     <row r="26" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="256" t="s">
         <v>481</v>
       </c>
       <c r="C26" s="244"/>
@@ -7971,7 +7993,7 @@
     </row>
     <row r="27" spans="2:5" ht="6" customHeight="1"/>
     <row r="28" spans="2:5" ht="18" customHeight="1">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="254" t="s">
         <v>482</v>
       </c>
       <c r="C28" s="244"/>
@@ -7979,7 +8001,7 @@
       <c r="E28" s="244"/>
     </row>
     <row r="29" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B29" s="259" t="s">
+      <c r="B29" s="255" t="s">
         <v>483</v>
       </c>
       <c r="C29" s="244"/>
@@ -7987,7 +8009,7 @@
       <c r="E29" s="244"/>
     </row>
     <row r="30" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B30" s="255" t="s">
+      <c r="B30" s="259" t="s">
         <v>476</v>
       </c>
       <c r="C30" s="244"/>
@@ -7995,7 +8017,7 @@
       <c r="E30" s="244"/>
     </row>
     <row r="31" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B31" s="254" t="s">
+      <c r="B31" s="256" t="s">
         <v>484</v>
       </c>
       <c r="C31" s="244"/>
@@ -8003,7 +8025,7 @@
       <c r="E31" s="244"/>
     </row>
     <row r="32" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B32" s="254" t="s">
+      <c r="B32" s="256" t="s">
         <v>485</v>
       </c>
       <c r="C32" s="244"/>
@@ -8011,7 +8033,7 @@
       <c r="E32" s="244"/>
     </row>
     <row r="33" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B33" s="254" t="s">
+      <c r="B33" s="256" t="s">
         <v>486</v>
       </c>
       <c r="C33" s="244"/>
@@ -8019,7 +8041,7 @@
       <c r="E33" s="244"/>
     </row>
     <row r="34" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B34" s="254" t="s">
+      <c r="B34" s="256" t="s">
         <v>487</v>
       </c>
       <c r="C34" s="244"/>
@@ -8027,7 +8049,7 @@
       <c r="E34" s="244"/>
     </row>
     <row r="35" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B35" s="254" t="s">
+      <c r="B35" s="256" t="s">
         <v>481</v>
       </c>
       <c r="C35" s="244"/>
@@ -8036,7 +8058,7 @@
     </row>
     <row r="36" spans="2:5" ht="6" customHeight="1"/>
     <row r="37" spans="2:5" ht="18" customHeight="1">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="254" t="s">
         <v>488</v>
       </c>
       <c r="C37" s="244"/>
@@ -8044,7 +8066,7 @@
       <c r="E37" s="244"/>
     </row>
     <row r="38" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B38" s="256" t="s">
+      <c r="B38" s="260" t="s">
         <v>489</v>
       </c>
       <c r="C38" s="244"/>
@@ -8052,7 +8074,7 @@
       <c r="E38" s="244"/>
     </row>
     <row r="39" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B39" s="255" t="s">
+      <c r="B39" s="259" t="s">
         <v>490</v>
       </c>
       <c r="C39" s="244"/>
@@ -8060,7 +8082,7 @@
       <c r="E39" s="244"/>
     </row>
     <row r="40" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="256" t="s">
         <v>491</v>
       </c>
       <c r="C40" s="244"/>
@@ -8068,7 +8090,7 @@
       <c r="E40" s="244"/>
     </row>
     <row r="41" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B41" s="254" t="s">
+      <c r="B41" s="256" t="s">
         <v>492</v>
       </c>
       <c r="C41" s="244"/>
@@ -8076,7 +8098,7 @@
       <c r="E41" s="244"/>
     </row>
     <row r="42" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C42" s="244"/>
@@ -8084,7 +8106,7 @@
       <c r="E42" s="244"/>
     </row>
     <row r="43" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B43" s="254" t="s">
+      <c r="B43" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C43" s="244"/>
@@ -8092,7 +8114,7 @@
       <c r="E43" s="244"/>
     </row>
     <row r="44" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B44" s="254" t="s">
+      <c r="B44" s="256" t="s">
         <v>495</v>
       </c>
       <c r="C44" s="244"/>
@@ -8117,7 +8139,7 @@
     </row>
     <row r="47" spans="2:5" ht="6" customHeight="1"/>
     <row r="48" spans="2:5" ht="18" customHeight="1">
-      <c r="B48" s="258" t="s">
+      <c r="B48" s="254" t="s">
         <v>498</v>
       </c>
       <c r="C48" s="244"/>
@@ -8125,7 +8147,7 @@
       <c r="E48" s="244"/>
     </row>
     <row r="49" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B49" s="256" t="s">
+      <c r="B49" s="260" t="s">
         <v>499</v>
       </c>
       <c r="C49" s="244"/>
@@ -8133,7 +8155,7 @@
       <c r="E49" s="244"/>
     </row>
     <row r="50" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B50" s="255" t="s">
+      <c r="B50" s="259" t="s">
         <v>490</v>
       </c>
       <c r="C50" s="244"/>
@@ -8141,7 +8163,7 @@
       <c r="E50" s="244"/>
     </row>
     <row r="51" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="256" t="s">
         <v>491</v>
       </c>
       <c r="C51" s="244"/>
@@ -8149,7 +8171,7 @@
       <c r="E51" s="244"/>
     </row>
     <row r="52" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B52" s="254" t="s">
+      <c r="B52" s="256" t="s">
         <v>500</v>
       </c>
       <c r="C52" s="244"/>
@@ -8157,7 +8179,7 @@
       <c r="E52" s="244"/>
     </row>
     <row r="53" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B53" s="254" t="s">
+      <c r="B53" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C53" s="244"/>
@@ -8165,7 +8187,7 @@
       <c r="E53" s="244"/>
     </row>
     <row r="54" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B54" s="254" t="s">
+      <c r="B54" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C54" s="244"/>
@@ -8173,7 +8195,7 @@
       <c r="E54" s="244"/>
     </row>
     <row r="55" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B55" s="254" t="s">
+      <c r="B55" s="256" t="s">
         <v>501</v>
       </c>
       <c r="C55" s="244"/>
@@ -8198,7 +8220,7 @@
     </row>
     <row r="58" spans="2:5" ht="6" customHeight="1"/>
     <row r="59" spans="2:5" ht="18" customHeight="1">
-      <c r="B59" s="258" t="s">
+      <c r="B59" s="254" t="s">
         <v>503</v>
       </c>
       <c r="C59" s="244"/>
@@ -8206,7 +8228,7 @@
       <c r="E59" s="244"/>
     </row>
     <row r="60" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B60" s="259" t="s">
+      <c r="B60" s="255" t="s">
         <v>504</v>
       </c>
       <c r="C60" s="244"/>
@@ -8630,7 +8652,7 @@
     </row>
     <row r="92" spans="2:5" ht="6" customHeight="1"/>
     <row r="93" spans="2:5" ht="18" customHeight="1">
-      <c r="B93" s="258" t="s">
+      <c r="B93" s="254" t="s">
         <v>519</v>
       </c>
       <c r="C93" s="244"/>
@@ -8638,7 +8660,7 @@
       <c r="E93" s="244"/>
     </row>
     <row r="94" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B94" s="259" t="s">
+      <c r="B94" s="255" t="s">
         <v>520</v>
       </c>
       <c r="C94" s="244"/>
@@ -8646,7 +8668,7 @@
       <c r="E94" s="244"/>
     </row>
     <row r="95" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B95" s="255" t="s">
+      <c r="B95" s="259" t="s">
         <v>521</v>
       </c>
       <c r="C95" s="244"/>
@@ -8654,7 +8676,7 @@
       <c r="E95" s="244"/>
     </row>
     <row r="96" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B96" s="254" t="s">
+      <c r="B96" s="256" t="s">
         <v>522</v>
       </c>
       <c r="C96" s="244"/>
@@ -8662,7 +8684,7 @@
       <c r="E96" s="244"/>
     </row>
     <row r="97" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B97" s="254" t="s">
+      <c r="B97" s="256" t="s">
         <v>523</v>
       </c>
       <c r="C97" s="244"/>
@@ -8670,7 +8692,7 @@
       <c r="E97" s="244"/>
     </row>
     <row r="98" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B98" s="254" t="s">
+      <c r="B98" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C98" s="244"/>
@@ -8678,7 +8700,7 @@
       <c r="E98" s="244"/>
     </row>
     <row r="99" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B99" s="254" t="s">
+      <c r="B99" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C99" s="244"/>
@@ -8686,7 +8708,7 @@
       <c r="E99" s="244"/>
     </row>
     <row r="100" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B100" s="254" t="s">
+      <c r="B100" s="256" t="s">
         <v>524</v>
       </c>
       <c r="C100" s="244"/>
@@ -8694,7 +8716,7 @@
       <c r="E100" s="244"/>
     </row>
     <row r="101" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B101" s="255" t="s">
+      <c r="B101" s="259" t="s">
         <v>525</v>
       </c>
       <c r="C101" s="244"/>
@@ -8719,7 +8741,7 @@
     </row>
     <row r="104" spans="2:5" ht="6" customHeight="1"/>
     <row r="105" spans="2:5" ht="18" customHeight="1">
-      <c r="B105" s="258" t="s">
+      <c r="B105" s="254" t="s">
         <v>528</v>
       </c>
       <c r="C105" s="244"/>
@@ -8727,7 +8749,7 @@
       <c r="E105" s="244"/>
     </row>
     <row r="106" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B106" s="259" t="s">
+      <c r="B106" s="255" t="s">
         <v>529</v>
       </c>
       <c r="C106" s="244"/>
@@ -8743,7 +8765,7 @@
       <c r="E107" s="244"/>
     </row>
     <row r="108" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B108" s="255" t="s">
+      <c r="B108" s="259" t="s">
         <v>490</v>
       </c>
       <c r="C108" s="244"/>
@@ -8751,7 +8773,7 @@
       <c r="E108" s="244"/>
     </row>
     <row r="109" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B109" s="254" t="s">
+      <c r="B109" s="256" t="s">
         <v>491</v>
       </c>
       <c r="C109" s="244"/>
@@ -8759,7 +8781,7 @@
       <c r="E109" s="244"/>
     </row>
     <row r="110" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B110" s="254" t="s">
+      <c r="B110" s="256" t="s">
         <v>531</v>
       </c>
       <c r="C110" s="244"/>
@@ -8767,7 +8789,7 @@
       <c r="E110" s="244"/>
     </row>
     <row r="111" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B111" s="254" t="s">
+      <c r="B111" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C111" s="244"/>
@@ -8775,7 +8797,7 @@
       <c r="E111" s="244"/>
     </row>
     <row r="112" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B112" s="254" t="s">
+      <c r="B112" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C112" s="244"/>
@@ -8783,7 +8805,7 @@
       <c r="E112" s="244"/>
     </row>
     <row r="113" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B113" s="254" t="s">
+      <c r="B113" s="256" t="s">
         <v>532</v>
       </c>
       <c r="C113" s="244"/>
@@ -8793,7 +8815,7 @@
     <row r="114" spans="2:5" ht="6" customHeight="1"/>
     <row r="115" spans="2:5" ht="6" customHeight="1"/>
     <row r="116" spans="2:5" ht="18" customHeight="1">
-      <c r="B116" s="258" t="s">
+      <c r="B116" s="254" t="s">
         <v>533</v>
       </c>
       <c r="C116" s="244"/>
@@ -8930,6 +8952,53 @@
     <row r="127" spans="2:5" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B100:E100"/>
     <mergeCell ref="B116:E116"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B112:E112"/>
@@ -8946,53 +9015,6 @@
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B93:E93"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B45:E45"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9015,8 +9037,8 @@
   <sheetData>
     <row r="1" spans="2:14" ht="6" customHeight="1"/>
     <row r="2" spans="2:14" ht="24" customHeight="1">
-      <c r="B2" s="260" t="s">
-        <v>712</v>
+      <c r="B2" s="258" t="s">
+        <v>708</v>
       </c>
       <c r="C2" s="244"/>
       <c r="D2" s="244"/>
@@ -9025,7 +9047,7 @@
     </row>
     <row r="3" spans="2:14" ht="6" customHeight="1"/>
     <row r="4" spans="2:14" ht="18" customHeight="1">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="254" t="s">
         <v>557</v>
       </c>
       <c r="C4" s="244"/>
@@ -9034,8 +9056,8 @@
       <c r="F4" s="244"/>
     </row>
     <row r="5" spans="2:14" ht="14.1" customHeight="1">
-      <c r="B5" s="266" t="s">
-        <v>716</v>
+      <c r="B5" s="262" t="s">
+        <v>712</v>
       </c>
       <c r="C5" s="244"/>
       <c r="D5" s="244"/>
@@ -9065,7 +9087,7 @@
         <v>563</v>
       </c>
       <c r="D8" s="173" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E8" s="164" t="s">
         <v>564</v>
@@ -9152,7 +9174,7 @@
         <v>574</v>
       </c>
       <c r="E12" s="171" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="H12" s="160"/>
       <c r="I12" s="160"/>
@@ -9172,7 +9194,7 @@
       <c r="N13" s="160"/>
     </row>
     <row r="14" spans="2:14" ht="18" customHeight="1">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="254" t="s">
         <v>575</v>
       </c>
       <c r="C14" s="244"/>
@@ -9188,7 +9210,7 @@
       <c r="N14" s="160"/>
     </row>
     <row r="15" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B15" s="255" t="s">
+      <c r="B15" s="259" t="s">
         <v>576</v>
       </c>
       <c r="C15" s="244"/>
@@ -9220,8 +9242,8 @@
       <c r="N16" s="160"/>
     </row>
     <row r="17" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B17" s="261" t="s">
-        <v>722</v>
+      <c r="B17" s="263" t="s">
+        <v>718</v>
       </c>
       <c r="C17" s="244"/>
       <c r="D17" s="244"/>
@@ -9236,8 +9258,8 @@
       <c r="N17" s="160"/>
     </row>
     <row r="18" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B18" s="261" t="s">
-        <v>717</v>
+      <c r="B18" s="263" t="s">
+        <v>713</v>
       </c>
       <c r="C18" s="244"/>
       <c r="D18" s="244"/>
@@ -9252,8 +9274,8 @@
       <c r="N18" s="160"/>
     </row>
     <row r="19" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B19" s="261" t="s">
-        <v>718</v>
+      <c r="B19" s="263" t="s">
+        <v>714</v>
       </c>
       <c r="C19" s="244"/>
       <c r="D19" s="244"/>
@@ -9261,7 +9283,7 @@
       <c r="F19" s="244"/>
     </row>
     <row r="20" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="256" t="s">
         <v>578</v>
       </c>
       <c r="C20" s="244"/>
@@ -9270,8 +9292,8 @@
       <c r="F20" s="244"/>
     </row>
     <row r="21" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B21" s="261" t="s">
-        <v>719</v>
+      <c r="B21" s="263" t="s">
+        <v>715</v>
       </c>
       <c r="C21" s="244"/>
       <c r="D21" s="244"/>
@@ -9279,8 +9301,8 @@
       <c r="F21" s="244"/>
     </row>
     <row r="22" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B22" s="261" t="s">
-        <v>721</v>
+      <c r="B22" s="263" t="s">
+        <v>717</v>
       </c>
       <c r="C22" s="244"/>
       <c r="D22" s="244"/>
@@ -9288,8 +9310,8 @@
       <c r="F22" s="244"/>
     </row>
     <row r="23" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B23" s="261" t="s">
-        <v>720</v>
+      <c r="B23" s="263" t="s">
+        <v>716</v>
       </c>
       <c r="C23" s="244"/>
       <c r="D23" s="244"/>
@@ -9297,7 +9319,7 @@
       <c r="F23" s="244"/>
     </row>
     <row r="24" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B24" s="254" t="s">
+      <c r="B24" s="256" t="s">
         <v>579</v>
       </c>
       <c r="C24" s="244"/>
@@ -9306,7 +9328,7 @@
       <c r="F24" s="244"/>
     </row>
     <row r="25" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B25" s="255" t="s">
+      <c r="B25" s="259" t="s">
         <v>580</v>
       </c>
       <c r="C25" s="244"/>
@@ -9324,7 +9346,7 @@
       <c r="F26" s="244"/>
     </row>
     <row r="27" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B27" s="254" t="s">
+      <c r="B27" s="256" t="s">
         <v>582</v>
       </c>
       <c r="C27" s="244"/>
@@ -9333,7 +9355,7 @@
       <c r="F27" s="244"/>
     </row>
     <row r="28" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="256" t="s">
         <v>583</v>
       </c>
       <c r="C28" s="244"/>
@@ -9342,7 +9364,7 @@
       <c r="F28" s="244"/>
     </row>
     <row r="29" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="256" t="s">
         <v>584</v>
       </c>
       <c r="C29" s="244"/>
@@ -9351,7 +9373,7 @@
       <c r="F29" s="244"/>
     </row>
     <row r="30" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B30" s="254" t="s">
+      <c r="B30" s="256" t="s">
         <v>585</v>
       </c>
       <c r="C30" s="244"/>
@@ -9360,7 +9382,7 @@
       <c r="F30" s="244"/>
     </row>
     <row r="31" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B31" s="254" t="s">
+      <c r="B31" s="256" t="s">
         <v>586</v>
       </c>
       <c r="C31" s="244"/>
@@ -9369,7 +9391,7 @@
       <c r="F31" s="244"/>
     </row>
     <row r="32" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B32" s="255" t="s">
+      <c r="B32" s="259" t="s">
         <v>587</v>
       </c>
       <c r="C32" s="244"/>
@@ -9387,7 +9409,7 @@
       <c r="F33" s="244"/>
     </row>
     <row r="34" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B34" s="254" t="s">
+      <c r="B34" s="256" t="s">
         <v>589</v>
       </c>
       <c r="C34" s="244"/>
@@ -9396,16 +9418,16 @@
       <c r="F34" s="244"/>
     </row>
     <row r="35" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B35" s="262" t="s">
-        <v>723</v>
-      </c>
-      <c r="C35" s="263"/>
-      <c r="D35" s="263"/>
-      <c r="E35" s="263"/>
-      <c r="F35" s="263"/>
+      <c r="B35" s="264" t="s">
+        <v>719</v>
+      </c>
+      <c r="C35" s="265"/>
+      <c r="D35" s="265"/>
+      <c r="E35" s="265"/>
+      <c r="F35" s="265"/>
     </row>
     <row r="36" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B36" s="254" t="s">
+      <c r="B36" s="256" t="s">
         <v>590</v>
       </c>
       <c r="C36" s="244"/>
@@ -9414,7 +9436,7 @@
       <c r="F36" s="244"/>
     </row>
     <row r="37" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="256" t="s">
         <v>591</v>
       </c>
       <c r="C37" s="244"/>
@@ -9423,7 +9445,7 @@
       <c r="F37" s="244"/>
     </row>
     <row r="38" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B38" s="254" t="s">
+      <c r="B38" s="256" t="s">
         <v>592</v>
       </c>
       <c r="C38" s="244"/>
@@ -9433,7 +9455,7 @@
     </row>
     <row r="39" spans="2:6" ht="6" customHeight="1"/>
     <row r="40" spans="2:6" ht="18" customHeight="1">
-      <c r="B40" s="258" t="s">
+      <c r="B40" s="254" t="s">
         <v>593</v>
       </c>
       <c r="C40" s="244"/>
@@ -9442,7 +9464,7 @@
       <c r="F40" s="244"/>
     </row>
     <row r="41" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B41" s="265" t="s">
+      <c r="B41" s="266" t="s">
         <v>594</v>
       </c>
       <c r="C41" s="244"/>
@@ -9469,7 +9491,7 @@
       </c>
     </row>
     <row r="44" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B44" s="264" t="s">
+      <c r="B44" s="261" t="s">
         <v>600</v>
       </c>
       <c r="C44" s="244"/>
@@ -9481,8 +9503,8 @@
       <c r="B45" s="171" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="171" t="s">
-        <v>601</v>
+      <c r="C45" s="267" t="s">
+        <v>778</v>
       </c>
       <c r="D45" s="171" t="s">
         <v>602</v>
@@ -9508,14 +9530,14 @@
       <c r="F46" s="164"/>
     </row>
     <row r="47" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B47" s="171" t="s">
+      <c r="B47" s="267" t="s">
+        <v>774</v>
+      </c>
+      <c r="C47" s="171" t="s">
         <v>607</v>
       </c>
-      <c r="C47" s="171" t="s">
+      <c r="D47" s="171" t="s">
         <v>608</v>
-      </c>
-      <c r="D47" s="171" t="s">
-        <v>609</v>
       </c>
       <c r="E47" s="171" t="s">
         <v>603</v>
@@ -9524,13 +9546,13 @@
     </row>
     <row r="48" spans="2:6" ht="14.1" customHeight="1">
       <c r="B48" s="164" t="s">
+        <v>609</v>
+      </c>
+      <c r="C48" s="164" t="s">
         <v>610</v>
       </c>
-      <c r="C48" s="164" t="s">
+      <c r="D48" s="164" t="s">
         <v>611</v>
-      </c>
-      <c r="D48" s="164" t="s">
-        <v>612</v>
       </c>
       <c r="E48" s="164" t="s">
         <v>603</v>
@@ -9539,13 +9561,13 @@
     </row>
     <row r="49" spans="2:6" ht="14.1" customHeight="1">
       <c r="B49" s="171" t="s">
+        <v>612</v>
+      </c>
+      <c r="C49" s="171" t="s">
         <v>613</v>
       </c>
-      <c r="C49" s="171" t="s">
+      <c r="D49" s="171" t="s">
         <v>614</v>
-      </c>
-      <c r="D49" s="171" t="s">
-        <v>615</v>
       </c>
       <c r="E49" s="171" t="s">
         <v>603</v>
@@ -9554,13 +9576,13 @@
     </row>
     <row r="50" spans="2:6" ht="14.1" customHeight="1">
       <c r="B50" s="164" t="s">
+        <v>615</v>
+      </c>
+      <c r="C50" s="164" t="s">
         <v>616</v>
       </c>
-      <c r="C50" s="164" t="s">
+      <c r="D50" s="164" t="s">
         <v>617</v>
-      </c>
-      <c r="D50" s="164" t="s">
-        <v>618</v>
       </c>
       <c r="E50" s="164" t="s">
         <v>603</v>
@@ -9568,8 +9590,8 @@
       <c r="F50" s="164"/>
     </row>
     <row r="51" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B51" s="264" t="s">
-        <v>619</v>
+      <c r="B51" s="261" t="s">
+        <v>618</v>
       </c>
       <c r="C51" s="244"/>
       <c r="D51" s="244"/>
@@ -9580,11 +9602,11 @@
       <c r="B52" s="164" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="164" t="s">
-        <v>620</v>
+      <c r="C52" s="173" t="s">
+        <v>777</v>
       </c>
       <c r="D52" s="164" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E52" s="164" t="s">
         <v>603</v>
@@ -9596,10 +9618,10 @@
         <v>87</v>
       </c>
       <c r="C53" s="171" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D53" s="171" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E53" s="171" t="s">
         <v>603</v>
@@ -9611,10 +9633,10 @@
         <v>243</v>
       </c>
       <c r="C54" s="164" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D54" s="164" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E54" s="164" t="s">
         <v>603</v>
@@ -9623,13 +9645,13 @@
     </row>
     <row r="55" spans="2:6" ht="14.1" customHeight="1">
       <c r="B55" s="171" t="s">
+        <v>624</v>
+      </c>
+      <c r="C55" s="171" t="s">
+        <v>625</v>
+      </c>
+      <c r="D55" s="171" t="s">
         <v>626</v>
-      </c>
-      <c r="C55" s="171" t="s">
-        <v>627</v>
-      </c>
-      <c r="D55" s="171" t="s">
-        <v>628</v>
       </c>
       <c r="E55" s="171" t="s">
         <v>603</v>
@@ -9637,8 +9659,8 @@
       <c r="F55" s="171"/>
     </row>
     <row r="56" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B56" s="264" t="s">
-        <v>629</v>
+      <c r="B56" s="261" t="s">
+        <v>627</v>
       </c>
       <c r="C56" s="244"/>
       <c r="D56" s="244"/>
@@ -9646,14 +9668,14 @@
       <c r="F56" s="244"/>
     </row>
     <row r="57" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B57" s="171" t="s">
-        <v>94</v>
+      <c r="B57" s="267" t="s">
+        <v>775</v>
       </c>
       <c r="C57" s="171" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D57" s="171" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E57" s="171" t="s">
         <v>603</v>
@@ -9662,13 +9684,13 @@
     </row>
     <row r="58" spans="2:6" ht="14.1" customHeight="1">
       <c r="B58" s="164" t="s">
+        <v>630</v>
+      </c>
+      <c r="C58" s="164" t="s">
+        <v>631</v>
+      </c>
+      <c r="D58" s="164" t="s">
         <v>632</v>
-      </c>
-      <c r="C58" s="164" t="s">
-        <v>633</v>
-      </c>
-      <c r="D58" s="164" t="s">
-        <v>634</v>
       </c>
       <c r="E58" s="164" t="s">
         <v>603</v>
@@ -9680,10 +9702,10 @@
         <v>265</v>
       </c>
       <c r="C59" s="171" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D59" s="171" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E59" s="171" t="s">
         <v>603</v>
@@ -9691,8 +9713,8 @@
       <c r="F59" s="171"/>
     </row>
     <row r="60" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B60" s="264" t="s">
-        <v>637</v>
+      <c r="B60" s="261" t="s">
+        <v>635</v>
       </c>
       <c r="C60" s="244"/>
       <c r="D60" s="244"/>
@@ -9704,10 +9726,10 @@
         <v>71</v>
       </c>
       <c r="C61" s="171" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D61" s="171" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E61" s="171" t="s">
         <v>603</v>
@@ -9719,10 +9741,10 @@
         <v>250</v>
       </c>
       <c r="C62" s="164" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D62" s="164" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E62" s="164" t="s">
         <v>603</v>
@@ -9730,14 +9752,14 @@
       <c r="F62" s="164"/>
     </row>
     <row r="63" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B63" s="171" t="s">
-        <v>253</v>
+      <c r="B63" s="267" t="s">
+        <v>779</v>
       </c>
       <c r="C63" s="171" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D63" s="171" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E63" s="171" t="s">
         <v>603</v>
@@ -9745,14 +9767,14 @@
       <c r="F63" s="171"/>
     </row>
     <row r="64" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B64" s="164" t="s">
-        <v>644</v>
+      <c r="B64" s="173" t="s">
+        <v>780</v>
       </c>
       <c r="C64" s="164" t="s">
         <v>604</v>
       </c>
       <c r="D64" s="164" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E64" s="164" t="s">
         <v>603</v>
@@ -9760,8 +9782,8 @@
       <c r="F64" s="164"/>
     </row>
     <row r="65" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B65" s="264" t="s">
-        <v>646</v>
+      <c r="B65" s="261" t="s">
+        <v>643</v>
       </c>
       <c r="C65" s="244"/>
       <c r="D65" s="244"/>
@@ -9773,28 +9795,28 @@
         <v>277</v>
       </c>
       <c r="C66" s="164" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D66" s="164" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E66" s="164" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F66" s="164"/>
     </row>
     <row r="67" spans="2:6" ht="14.1" customHeight="1">
       <c r="B67" s="171" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C67" s="171" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D67" s="171" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E67" s="171" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F67" s="171"/>
     </row>
@@ -9803,10 +9825,10 @@
         <v>104</v>
       </c>
       <c r="C68" s="164" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D68" s="164" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E68" s="164" t="s">
         <v>603</v>
@@ -9814,8 +9836,8 @@
       <c r="F68" s="164"/>
     </row>
     <row r="69" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B69" s="264" t="s">
-        <v>655</v>
+      <c r="B69" s="268" t="s">
+        <v>776</v>
       </c>
       <c r="C69" s="244"/>
       <c r="D69" s="244"/>
@@ -9827,10 +9849,10 @@
         <v>220</v>
       </c>
       <c r="C70" s="164" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D70" s="164" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E70" s="164" t="s">
         <v>603</v>
@@ -9842,10 +9864,10 @@
         <v>223</v>
       </c>
       <c r="C71" s="171" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D71" s="171" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E71" s="171" t="s">
         <v>603</v>
@@ -9857,10 +9879,10 @@
         <v>224</v>
       </c>
       <c r="C72" s="164" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E72" s="164" t="s">
         <v>603</v>
@@ -9868,8 +9890,8 @@
       <c r="F72" s="164"/>
     </row>
     <row r="73" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B73" s="264" t="s">
-        <v>661</v>
+      <c r="B73" s="261" t="s">
+        <v>657</v>
       </c>
       <c r="C73" s="244"/>
       <c r="D73" s="244"/>
@@ -9878,13 +9900,13 @@
     </row>
     <row r="74" spans="2:6" ht="14.1" customHeight="1">
       <c r="B74" s="164" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C74" s="164" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D74" s="164" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E74" s="164" t="s">
         <v>603</v>
@@ -9893,13 +9915,13 @@
     </row>
     <row r="75" spans="2:6" ht="14.1" customHeight="1">
       <c r="B75" s="171" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C75" s="171" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D75" s="171" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E75" s="171" t="s">
         <v>603</v>
@@ -9908,13 +9930,13 @@
     </row>
     <row r="76" spans="2:6" ht="14.1" customHeight="1">
       <c r="B76" s="164" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C76" s="164" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D76" s="164" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E76" s="164" t="s">
         <v>603</v>
@@ -9929,7 +9951,7 @@
         <v>601</v>
       </c>
       <c r="D77" s="171" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E77" s="171" t="s">
         <v>603</v>
@@ -9941,10 +9963,10 @@
         <v>287</v>
       </c>
       <c r="C78" s="164" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D78" s="164" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E78" s="164" t="s">
         <v>603</v>
@@ -9956,10 +9978,10 @@
         <v>284</v>
       </c>
       <c r="C79" s="171" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D79" s="171" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E79" s="171" t="s">
         <v>603</v>
@@ -9968,13 +9990,13 @@
     </row>
     <row r="80" spans="2:6" ht="14.1" customHeight="1">
       <c r="B80" s="164" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C80" s="164" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D80" s="164" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E80" s="164" t="s">
         <v>603</v>
@@ -9983,13 +10005,13 @@
     </row>
     <row r="81" spans="2:6" ht="14.1" customHeight="1">
       <c r="B81" s="171" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C81" s="171" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D81" s="171" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E81" s="171" t="s">
         <v>603</v>
@@ -10001,10 +10023,10 @@
         <v>315</v>
       </c>
       <c r="C82" s="164" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D82" s="164" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E82" s="164" t="s">
         <v>603</v>
@@ -10016,10 +10038,10 @@
         <v>328</v>
       </c>
       <c r="C83" s="171" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D83" s="171" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="E83" s="171" t="s">
         <v>603</v>
@@ -10031,10 +10053,10 @@
         <v>329</v>
       </c>
       <c r="C84" s="164" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D84" s="164" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E84" s="164" t="s">
         <v>603</v>
@@ -10042,8 +10064,8 @@
       <c r="F84" s="164"/>
     </row>
     <row r="85" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B85" s="264" t="s">
-        <v>680</v>
+      <c r="B85" s="261" t="s">
+        <v>676</v>
       </c>
       <c r="C85" s="244"/>
       <c r="D85" s="244"/>
@@ -10052,38 +10074,38 @@
     </row>
     <row r="86" spans="2:6" ht="27.95" customHeight="1">
       <c r="B86" s="164" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C86" s="164" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D86" s="164" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E86" s="164" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F86" s="164"/>
     </row>
     <row r="87" spans="2:6" ht="27.95" customHeight="1">
       <c r="B87" s="171" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C87" s="171" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D87" s="171" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E87" s="171" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F87" s="171"/>
     </row>
     <row r="88" spans="2:6" ht="6" customHeight="1"/>
     <row r="89" spans="2:6" ht="18" customHeight="1">
-      <c r="B89" s="258" t="s">
-        <v>688</v>
+      <c r="B89" s="254" t="s">
+        <v>684</v>
       </c>
       <c r="C89" s="244"/>
       <c r="D89" s="244"/>
@@ -10096,10 +10118,10 @@
         <v>386</v>
       </c>
       <c r="C91" s="163" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D91" s="163" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="E91" s="163" t="s">
         <v>23</v>
@@ -10107,94 +10129,103 @@
     </row>
     <row r="92" spans="2:6" ht="14.1" customHeight="1">
       <c r="B92" s="164" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C92" s="164" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D92" s="164" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E92" s="164" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="93" spans="2:6" ht="14.1" customHeight="1">
       <c r="B93" s="171" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C93" s="171" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D93" s="171" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E93" s="171"/>
     </row>
     <row r="94" spans="2:6" ht="14.1" customHeight="1">
       <c r="B94" s="164" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C94" s="164" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D94" s="164" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E94" s="164" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="95" spans="2:6" ht="14.1" customHeight="1">
       <c r="B95" s="171" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C95" s="171" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D95" s="171" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E95" s="171" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="96" spans="2:6" ht="14.1" customHeight="1">
       <c r="B96" s="164" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C96" s="164" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="D96" s="164" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E96" s="164" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="97" spans="2:5" ht="14.1" customHeight="1">
       <c r="B97" s="171" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C97" s="171" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D97" s="171" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="E97" s="171"/>
     </row>
     <row r="98" spans="2:5" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B38:F38"/>
@@ -10211,22 +10242,13 @@
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10266,15 +10288,15 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" customHeight="1">
       <c r="B3" s="4"/>
-      <c r="C3" s="204" t="s">
+      <c r="C3" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="205"/>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="205"/>
-      <c r="I3" s="205"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
       <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10" ht="15.95" customHeight="1">
@@ -10290,15 +10312,15 @@
     </row>
     <row r="5" spans="2:10" ht="31.5" customHeight="1">
       <c r="B5" s="6"/>
-      <c r="C5" s="206" t="s">
+      <c r="C5" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="205"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="2:10" ht="15.95" customHeight="1">
@@ -10326,11 +10348,11 @@
       <c r="F7" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="207" t="s">
+      <c r="G7" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="208"/>
-      <c r="I7" s="209"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="212"/>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="2:10" ht="15.95" customHeight="1">
@@ -10361,7 +10383,7 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="200" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="H9" s="201"/>
       <c r="I9" s="202"/>
@@ -10378,7 +10400,7 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="200" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="H10" s="201"/>
       <c r="I10" s="202"/>
@@ -10395,7 +10417,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="200" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H11" s="201"/>
       <c r="I11" s="202"/>
@@ -10715,9 +10737,9 @@
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="210"/>
-      <c r="H40" s="211"/>
-      <c r="I40" s="212"/>
+      <c r="G40" s="204"/>
+      <c r="H40" s="205"/>
+      <c r="I40" s="206"/>
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10" ht="15.95" customHeight="1">
@@ -10733,6 +10755,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G33:I33"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="G21:I21"/>
@@ -10749,26 +10791,6 @@
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="G7:I7"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -16839,23 +16861,23 @@
         <v>23</v>
       </c>
       <c r="J1" s="107" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="L1" s="143"/>
     </row>
     <row r="2" spans="1:12" ht="15.95" hidden="1" customHeight="1">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="241"/>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
     </row>
     <row r="3" spans="1:12" ht="15" hidden="1" customHeight="1">
       <c r="A3" s="92" t="s">
@@ -17019,10 +17041,10 @@
       </c>
       <c r="B9" s="237"/>
       <c r="C9" s="237"/>
-      <c r="D9" s="238"/>
+      <c r="D9" s="240"/>
       <c r="E9" s="237"/>
       <c r="F9" s="237"/>
-      <c r="G9" s="238"/>
+      <c r="G9" s="240"/>
       <c r="H9" s="237"/>
       <c r="I9" s="237"/>
       <c r="J9" s="156"/>
@@ -17491,15 +17513,15 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A26" s="239" t="s">
+      <c r="A26" s="241" t="s">
         <v>311</v>
       </c>
       <c r="B26" s="237"/>
       <c r="C26" s="237"/>
-      <c r="D26" s="238"/>
+      <c r="D26" s="240"/>
       <c r="E26" s="237"/>
       <c r="F26" s="237"/>
-      <c r="G26" s="238"/>
+      <c r="G26" s="240"/>
       <c r="H26" s="237"/>
       <c r="I26" s="237"/>
       <c r="J26" s="156"/>
@@ -17799,15 +17821,15 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A38" s="239" t="s">
+      <c r="A38" s="241" t="s">
         <v>324</v>
       </c>
       <c r="B38" s="237"/>
       <c r="C38" s="237"/>
-      <c r="D38" s="238"/>
+      <c r="D38" s="240"/>
       <c r="E38" s="237"/>
       <c r="F38" s="237"/>
-      <c r="G38" s="238"/>
+      <c r="G38" s="240"/>
       <c r="H38" s="237"/>
       <c r="I38" s="237"/>
       <c r="J38" s="156"/>
@@ -18095,15 +18117,15 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A49" s="239" t="s">
+      <c r="A49" s="241" t="s">
         <v>332</v>
       </c>
       <c r="B49" s="237"/>
       <c r="C49" s="237"/>
-      <c r="D49" s="238"/>
+      <c r="D49" s="240"/>
       <c r="E49" s="237"/>
       <c r="F49" s="237"/>
-      <c r="G49" s="238"/>
+      <c r="G49" s="240"/>
       <c r="H49" s="237"/>
       <c r="I49" s="237"/>
       <c r="J49" s="156"/>
@@ -18167,15 +18189,15 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A52" s="239" t="s">
+      <c r="A52" s="241" t="s">
         <v>335</v>
       </c>
       <c r="B52" s="237"/>
       <c r="C52" s="237"/>
-      <c r="D52" s="238"/>
+      <c r="D52" s="240"/>
       <c r="E52" s="237"/>
       <c r="F52" s="237"/>
-      <c r="G52" s="238"/>
+      <c r="G52" s="240"/>
       <c r="H52" s="237"/>
       <c r="I52" s="237"/>
       <c r="J52" s="156"/>
@@ -18298,15 +18320,15 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A57" s="239" t="s">
+      <c r="A57" s="241" t="s">
         <v>342</v>
       </c>
       <c r="B57" s="237"/>
       <c r="C57" s="237"/>
-      <c r="D57" s="238"/>
+      <c r="D57" s="240"/>
       <c r="E57" s="237"/>
       <c r="F57" s="237"/>
-      <c r="G57" s="238"/>
+      <c r="G57" s="240"/>
       <c r="H57" s="237"/>
       <c r="I57" s="237"/>
       <c r="J57" s="156"/>
@@ -18447,15 +18469,15 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A63" s="239" t="s">
+      <c r="A63" s="241" t="s">
         <v>348</v>
       </c>
       <c r="B63" s="237"/>
       <c r="C63" s="237"/>
-      <c r="D63" s="238"/>
+      <c r="D63" s="240"/>
       <c r="E63" s="237"/>
       <c r="F63" s="237"/>
-      <c r="G63" s="238"/>
+      <c r="G63" s="240"/>
       <c r="H63" s="237"/>
       <c r="I63" s="237"/>
       <c r="J63" s="156"/>
@@ -18488,15 +18510,15 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A65" s="239" t="s">
+      <c r="A65" s="241" t="s">
         <v>350</v>
       </c>
       <c r="B65" s="237"/>
       <c r="C65" s="237"/>
-      <c r="D65" s="238"/>
+      <c r="D65" s="240"/>
       <c r="E65" s="237"/>
       <c r="F65" s="237"/>
-      <c r="G65" s="238"/>
+      <c r="G65" s="240"/>
       <c r="H65" s="237"/>
       <c r="I65" s="237"/>
       <c r="J65" s="156"/>
@@ -18583,15 +18605,15 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A69" s="239" t="s">
+      <c r="A69" s="241" t="s">
         <v>354</v>
       </c>
       <c r="B69" s="237"/>
       <c r="C69" s="237"/>
-      <c r="D69" s="238"/>
+      <c r="D69" s="240"/>
       <c r="E69" s="237"/>
       <c r="F69" s="237"/>
-      <c r="G69" s="238"/>
+      <c r="G69" s="240"/>
       <c r="H69" s="237"/>
       <c r="I69" s="237"/>
       <c r="J69" s="156"/>
@@ -18706,15 +18728,15 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="239" t="s">
+      <c r="A74" s="241" t="s">
         <v>359</v>
       </c>
       <c r="B74" s="237"/>
       <c r="C74" s="237"/>
-      <c r="D74" s="238"/>
+      <c r="D74" s="240"/>
       <c r="E74" s="237"/>
       <c r="F74" s="237"/>
-      <c r="G74" s="238"/>
+      <c r="G74" s="240"/>
       <c r="H74" s="237"/>
       <c r="I74" s="237"/>
       <c r="J74" s="156"/>
@@ -18748,21 +18770,6 @@
   </sheetData>
   <autoFilter ref="C1:G75"/>
   <mergeCells count="31">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A49:C49"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A52:C52"/>
@@ -18779,6 +18786,21 @@
     <mergeCell ref="G49:I49"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="G74:I74"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A49:C49"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18835,7 +18857,7 @@
         <v>362</v>
       </c>
       <c r="K1" s="107" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.5" customHeight="1">
@@ -18854,7 +18876,7 @@
       <c r="K2" s="106"/>
     </row>
     <row r="3" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A3" s="238" t="s">
+      <c r="A3" s="240" t="s">
         <v>364</v>
       </c>
       <c r="B3" s="237"/>
@@ -18900,10 +18922,10 @@
         <v>26</v>
       </c>
       <c r="K4" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="M4" s="85" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16.5" customHeight="1">
@@ -18938,10 +18960,10 @@
         <v>26</v>
       </c>
       <c r="K5" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="M5" s="158" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16.5" customHeight="1">
@@ -18976,10 +18998,10 @@
         <v>26</v>
       </c>
       <c r="K6" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="M6" s="85" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16.5" customHeight="1">
@@ -19014,14 +19036,14 @@
         <v>26</v>
       </c>
       <c r="K7" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="M7" s="158" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A8" s="238" t="s">
+      <c r="A8" s="240" t="s">
         <v>370</v>
       </c>
       <c r="B8" s="237"/>
@@ -19037,7 +19059,7 @@
     </row>
     <row r="9" spans="1:13" ht="16.5" customHeight="1">
       <c r="A9" s="89" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B9" s="65" t="s">
         <v>26</v>
@@ -19067,11 +19089,11 @@
         <v>26</v>
       </c>
       <c r="K9" s="89" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A10" s="238" t="s">
+      <c r="A10" s="240" t="s">
         <v>371</v>
       </c>
       <c r="B10" s="237"/>
@@ -19117,7 +19139,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="89" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16.5" customHeight="1">
@@ -19152,11 +19174,11 @@
         <v>26</v>
       </c>
       <c r="K12" s="89" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A13" s="238" t="s">
+      <c r="A13" s="240" t="s">
         <v>372</v>
       </c>
       <c r="B13" s="237"/>
@@ -19202,7 +19224,7 @@
         <v>33</v>
       </c>
       <c r="K14" s="89" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16.5" customHeight="1">
@@ -19237,11 +19259,11 @@
         <v>33</v>
       </c>
       <c r="K15" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A16" s="238" t="s">
+      <c r="A16" s="240" t="s">
         <v>373</v>
       </c>
       <c r="B16" s="237"/>
@@ -19287,7 +19309,7 @@
         <v>33</v>
       </c>
       <c r="K17" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.5" customHeight="1">
@@ -19322,7 +19344,7 @@
         <v>33</v>
       </c>
       <c r="K18" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
@@ -19342,7 +19364,7 @@
       <c r="N19" s="144"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A20" s="239" t="s">
+      <c r="A20" s="241" t="s">
         <v>374</v>
       </c>
       <c r="B20" s="237"/>
@@ -19358,7 +19380,7 @@
     </row>
     <row r="21" spans="1:14" ht="22.5" customHeight="1">
       <c r="A21" s="89" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B21" s="65" t="s">
         <v>26</v>
@@ -19388,11 +19410,11 @@
         <v>33</v>
       </c>
       <c r="K21" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A22" s="239" t="s">
+      <c r="A22" s="241" t="s">
         <v>279</v>
       </c>
       <c r="B22" s="237"/>
@@ -19438,7 +19460,7 @@
         <v>33</v>
       </c>
       <c r="K23" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -19473,7 +19495,7 @@
         <v>33</v>
       </c>
       <c r="K24" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -19508,7 +19530,7 @@
         <v>33</v>
       </c>
       <c r="K25" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -19543,7 +19565,7 @@
         <v>33</v>
       </c>
       <c r="K26" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
@@ -19578,7 +19600,7 @@
         <v>33</v>
       </c>
       <c r="K27" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="16.5" customHeight="1">
@@ -19613,7 +19635,7 @@
         <v>33</v>
       </c>
       <c r="K28" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="16.5" customHeight="1">
@@ -19648,7 +19670,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="16.5" customHeight="1">
@@ -19683,7 +19705,7 @@
         <v>33</v>
       </c>
       <c r="K30" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1">
@@ -19718,7 +19740,7 @@
         <v>33</v>
       </c>
       <c r="K31" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="16.5" customHeight="1">
@@ -19753,7 +19775,7 @@
         <v>33</v>
       </c>
       <c r="K32" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
@@ -19788,7 +19810,7 @@
         <v>33</v>
       </c>
       <c r="K33" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1">
@@ -19823,11 +19845,11 @@
         <v>33</v>
       </c>
       <c r="K34" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A35" s="239" t="s">
+      <c r="A35" s="241" t="s">
         <v>317</v>
       </c>
       <c r="B35" s="237"/>
@@ -19873,7 +19895,7 @@
         <v>26</v>
       </c>
       <c r="K36" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="16.5" customHeight="1">
@@ -19908,11 +19930,11 @@
         <v>26</v>
       </c>
       <c r="K37" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="239" t="s">
+      <c r="A38" s="241" t="s">
         <v>324</v>
       </c>
       <c r="B38" s="237"/>
@@ -19958,7 +19980,7 @@
         <v>26</v>
       </c>
       <c r="K39" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="16.5" customHeight="1">
@@ -19993,7 +20015,7 @@
         <v>26</v>
       </c>
       <c r="K40" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="16.5" customHeight="1">
@@ -20028,11 +20050,11 @@
         <v>26</v>
       </c>
       <c r="K41" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="239" t="s">
+      <c r="A42" s="241" t="s">
         <v>379</v>
       </c>
       <c r="B42" s="237"/>
@@ -20078,7 +20100,7 @@
         <v>26</v>
       </c>
       <c r="K43" s="89" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="16.5" customHeight="1">
@@ -20113,11 +20135,11 @@
         <v>26</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A45" s="239" t="s">
+      <c r="A45" s="241" t="s">
         <v>335</v>
       </c>
       <c r="B45" s="237"/>
@@ -20163,7 +20185,7 @@
         <v>33</v>
       </c>
       <c r="K46" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="16.5" customHeight="1">
@@ -20198,7 +20220,7 @@
         <v>33</v>
       </c>
       <c r="K47" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="16.5" customHeight="1">
@@ -20233,7 +20255,7 @@
         <v>33</v>
       </c>
       <c r="K48" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="16.5" customHeight="1">
@@ -20268,11 +20290,11 @@
         <v>33</v>
       </c>
       <c r="K49" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A50" s="239" t="s">
+      <c r="A50" s="241" t="s">
         <v>348</v>
       </c>
       <c r="B50" s="237"/>
@@ -20318,11 +20340,11 @@
         <v>33</v>
       </c>
       <c r="K51" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A52" s="239" t="s">
+      <c r="A52" s="241" t="s">
         <v>350</v>
       </c>
       <c r="B52" s="237"/>
@@ -20368,7 +20390,7 @@
         <v>26</v>
       </c>
       <c r="K53" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="16.5" customHeight="1">
@@ -20403,7 +20425,7 @@
         <v>26</v>
       </c>
       <c r="K54" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="16.5" customHeight="1">
@@ -20436,11 +20458,11 @@
         <v>26</v>
       </c>
       <c r="K55" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A56" s="239" t="s">
+      <c r="A56" s="241" t="s">
         <v>354</v>
       </c>
       <c r="B56" s="237"/>
@@ -20486,7 +20508,7 @@
         <v>26</v>
       </c>
       <c r="K57" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="16.5" customHeight="1">
@@ -20521,7 +20543,7 @@
         <v>26</v>
       </c>
       <c r="K58" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="16.5" customHeight="1">
@@ -20556,11 +20578,11 @@
         <v>26</v>
       </c>
       <c r="K59" s="89" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A60" s="239" t="s">
+      <c r="A60" s="241" t="s">
         <v>384</v>
       </c>
       <c r="B60" s="237"/>
@@ -20606,7 +20628,7 @@
         <v>33</v>
       </c>
       <c r="K61" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="16.5" customHeight="1">
@@ -20641,7 +20663,7 @@
         <v>33</v>
       </c>
       <c r="K62" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="16.5" customHeight="1">
@@ -20676,7 +20698,7 @@
         <v>33</v>
       </c>
       <c r="K63" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="16.5" customHeight="1">
@@ -20711,7 +20733,7 @@
         <v>33</v>
       </c>
       <c r="K64" s="89" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="65" spans="8:8" ht="12" customHeight="1">
@@ -20720,13 +20742,6 @@
   </sheetData>
   <autoFilter ref="B1:F1"/>
   <mergeCells count="17">
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A52:H52"/>
@@ -20737,6 +20752,13 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A56:H56"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20762,7 +20784,7 @@
     <row r="1" spans="2:6" ht="6" customHeight="1"/>
     <row r="2" spans="2:6" ht="24" customHeight="1">
       <c r="B2" s="245" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C2" s="244"/>
       <c r="D2" s="244"/>
@@ -20772,7 +20794,7 @@
     <row r="3" spans="2:6" ht="6" customHeight="1"/>
     <row r="4" spans="2:6" ht="18" customHeight="1">
       <c r="B4" s="243" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C4" s="244"/>
       <c r="D4" s="244"/>
@@ -20787,10 +20809,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="185" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E5" s="185" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>387</v>
@@ -20801,30 +20823,30 @@
         <v>190</v>
       </c>
       <c r="C6" s="187" t="s">
+        <v>748</v>
+      </c>
+      <c r="D6" s="187" t="s">
         <v>752</v>
       </c>
-      <c r="D6" s="187" t="s">
-        <v>756</v>
-      </c>
       <c r="E6" s="187" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F6" s="188" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="54">
       <c r="B7" s="189" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C7" s="190" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="D7" s="190" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E7" s="190" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F7" s="191" t="s">
         <v>388</v>
@@ -20832,16 +20854,16 @@
     </row>
     <row r="8" spans="2:6" ht="54">
       <c r="B8" s="186" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C8" s="187" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="D8" s="187" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="E8" s="187" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="F8" s="192" t="s">
         <v>388</v>
@@ -20850,7 +20872,7 @@
     <row r="9" spans="2:6" ht="6" customHeight="1"/>
     <row r="10" spans="2:6" ht="18" customHeight="1">
       <c r="B10" s="243" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C10" s="244"/>
       <c r="D10" s="244"/>
@@ -20865,10 +20887,10 @@
         <v>18</v>
       </c>
       <c r="D11" s="185" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E11" s="185" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F11" s="185" t="s">
         <v>387</v>
@@ -20876,7 +20898,7 @@
     </row>
     <row r="12" spans="2:6" ht="12.95" customHeight="1">
       <c r="B12" s="246" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C12" s="244"/>
       <c r="D12" s="244"/>
@@ -20885,16 +20907,16 @@
     </row>
     <row r="13" spans="2:6" ht="54">
       <c r="B13" s="186" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C13" s="187" t="s">
         <v>389</v>
       </c>
       <c r="D13" s="187" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E13" s="187" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F13" s="193" t="s">
         <v>390</v>
@@ -20902,16 +20924,16 @@
     </row>
     <row r="14" spans="2:6" ht="54">
       <c r="B14" s="189" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C14" s="190" t="s">
         <v>377</v>
       </c>
       <c r="D14" s="190" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E14" s="190" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F14" s="194" t="s">
         <v>390</v>
@@ -20919,16 +20941,16 @@
     </row>
     <row r="15" spans="2:6" ht="94.5">
       <c r="B15" s="186" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C15" s="187" t="s">
         <v>378</v>
       </c>
       <c r="D15" s="187" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E15" s="187" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>390</v>
@@ -20936,16 +20958,16 @@
     </row>
     <row r="16" spans="2:6" ht="67.5">
       <c r="B16" s="189" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C16" s="190" t="s">
         <v>391</v>
       </c>
       <c r="D16" s="190" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E16" s="190" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F16" s="194" t="s">
         <v>390</v>
@@ -20954,7 +20976,7 @@
     <row r="17" spans="2:6" ht="6" customHeight="1"/>
     <row r="18" spans="2:6" ht="18" customHeight="1">
       <c r="B18" s="243" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C18" s="244"/>
       <c r="D18" s="244"/>
@@ -20969,10 +20991,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="185" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E19" s="185" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F19" s="185" t="s">
         <v>387</v>
@@ -20986,10 +21008,10 @@
         <v>393</v>
       </c>
       <c r="D20" s="187" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E20" s="187" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F20" s="193" t="s">
         <v>390</v>
@@ -20998,7 +21020,7 @@
     <row r="21" spans="2:6" ht="6" customHeight="1"/>
     <row r="22" spans="2:6" ht="18" customHeight="1">
       <c r="B22" s="243" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C22" s="244"/>
       <c r="D22" s="244"/>
@@ -21013,10 +21035,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="185" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E23" s="185" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F23" s="185" t="s">
         <v>387</v>
@@ -21027,13 +21049,13 @@
         <v>394</v>
       </c>
       <c r="C24" s="187" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D24" s="187" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E24" s="187" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="F24" s="192" t="s">
         <v>388</v>
@@ -21044,13 +21066,13 @@
         <v>395</v>
       </c>
       <c r="C25" s="190" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="D25" s="190" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E25" s="190" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F25" s="195" t="s">
         <v>396</v>

--- a/DOC/EM&REM/(분석,방안) NexacroK-상대단위(em,rem) 확장 지원.xlsx
+++ b/DOC/EM&REM/(분석,방안) NexacroK-상대단위(em,rem) 확장 지원.xlsx
@@ -212,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="782">
   <si>
     <t>문서 이력 정보(Revision History)</t>
   </si>
@@ -2160,16 +2160,10 @@
     <t>A</t>
   </si>
   <si>
-    <t>background-position</t>
-  </si>
-  <si>
     <t>1em 0.5em</t>
   </si>
   <si>
     <t>background-position em/rem 환산 적용</t>
-  </si>
-  <si>
-    <t>0.2em 0.2em 0.5rem rgba(0,0,0,0.3)</t>
   </si>
   <si>
     <t>offset-x/y/blur em·rem 환산 후 DOM box-shadow 적용</t>
@@ -2881,6 +2875,18 @@
   </si>
   <si>
     <t>line-spacing</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>background-position</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>boxShadow</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2em 0.2em 0.5rem rgba(0,0,0,0.3)</t>
     <phoneticPr fontId="37" type="noConversion"/>
   </si>
 </sst>
@@ -5550,6 +5556,9 @@
     <xf numFmtId="0" fontId="81" fillId="32" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5570,25 +5579,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5634,16 +5643,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5657,26 +5666,38 @@
     <xf numFmtId="0" fontId="50" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5684,44 +5705,29 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="32" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="266">
@@ -6856,15 +6862,15 @@
     <row r="13" spans="1:11" ht="20.25">
       <c r="A13" s="174"/>
       <c r="B13" s="178"/>
-      <c r="C13" s="196" t="s">
-        <v>722</v>
-      </c>
-      <c r="D13" s="197"/>
-      <c r="E13" s="197"/>
-      <c r="F13" s="197"/>
-      <c r="G13" s="197"/>
-      <c r="H13" s="197"/>
-      <c r="I13" s="197"/>
+      <c r="C13" s="197" t="s">
+        <v>720</v>
+      </c>
+      <c r="D13" s="198"/>
+      <c r="E13" s="198"/>
+      <c r="F13" s="198"/>
+      <c r="G13" s="198"/>
+      <c r="H13" s="198"/>
+      <c r="I13" s="198"/>
       <c r="J13" s="180"/>
       <c r="K13" s="174"/>
     </row>
@@ -6884,15 +6890,15 @@
     <row r="15" spans="1:11">
       <c r="A15" s="174"/>
       <c r="B15" s="178"/>
-      <c r="C15" s="198" t="s">
-        <v>720</v>
-      </c>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-      <c r="F15" s="198"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="198"/>
-      <c r="I15" s="198"/>
+      <c r="C15" s="199" t="s">
+        <v>718</v>
+      </c>
+      <c r="D15" s="199"/>
+      <c r="E15" s="199"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="199"/>
+      <c r="H15" s="199"/>
+      <c r="I15" s="199"/>
       <c r="J15" s="180"/>
       <c r="K15" s="174"/>
     </row>
@@ -7159,15 +7165,15 @@
     <row r="36" spans="1:11">
       <c r="A36" s="174"/>
       <c r="B36" s="178"/>
-      <c r="C36" s="199" t="s">
-        <v>721</v>
-      </c>
-      <c r="D36" s="199"/>
-      <c r="E36" s="199"/>
-      <c r="F36" s="199"/>
-      <c r="G36" s="199"/>
-      <c r="H36" s="199"/>
-      <c r="I36" s="199"/>
+      <c r="C36" s="200" t="s">
+        <v>719</v>
+      </c>
+      <c r="D36" s="200"/>
+      <c r="E36" s="200"/>
+      <c r="F36" s="200"/>
+      <c r="G36" s="200"/>
+      <c r="H36" s="200"/>
+      <c r="I36" s="200"/>
       <c r="J36" s="180"/>
       <c r="K36" s="174"/>
     </row>
@@ -7273,35 +7279,35 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1"/>
     <row r="2" spans="2:4" ht="21.95" customHeight="1">
-      <c r="B2" s="253" t="s">
+      <c r="B2" s="252" t="s">
         <v>397</v>
       </c>
-      <c r="C2" s="244"/>
+      <c r="C2" s="245"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1"/>
     <row r="4" spans="2:4" ht="18" customHeight="1">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="251" t="s">
         <v>398</v>
       </c>
-      <c r="C4" s="244"/>
+      <c r="C4" s="245"/>
     </row>
     <row r="5" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B5" s="250" t="s">
+      <c r="B5" s="248" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="244"/>
+      <c r="C5" s="245"/>
     </row>
     <row r="6" spans="2:4" ht="14.1" customHeight="1">
-      <c r="B6" s="249" t="s">
+      <c r="B6" s="250" t="s">
         <v>400</v>
       </c>
-      <c r="C6" s="244"/>
+      <c r="C6" s="245"/>
     </row>
     <row r="7" spans="2:4" ht="14.1" customHeight="1">
-      <c r="B7" s="249" t="s">
+      <c r="B7" s="250" t="s">
         <v>401</v>
       </c>
-      <c r="C7" s="244"/>
+      <c r="C7" s="245"/>
     </row>
     <row r="9" spans="2:4">
       <c r="C9" s="85" t="s">
@@ -7314,101 +7320,101 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B13" s="250" t="s">
+      <c r="B13" s="248" t="s">
         <v>404</v>
       </c>
-      <c r="C13" s="244"/>
+      <c r="C13" s="245"/>
     </row>
     <row r="14" spans="2:4" ht="14.1" customHeight="1">
-      <c r="B14" s="249" t="s">
+      <c r="B14" s="250" t="s">
         <v>405</v>
       </c>
-      <c r="C14" s="244"/>
+      <c r="C14" s="245"/>
     </row>
     <row r="15" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B15" s="250" t="s">
+      <c r="B15" s="248" t="s">
         <v>406</v>
       </c>
-      <c r="C15" s="244"/>
+      <c r="C15" s="245"/>
     </row>
     <row r="16" spans="2:4" ht="14.1" customHeight="1">
-      <c r="B16" s="249" t="s">
+      <c r="B16" s="250" t="s">
         <v>407</v>
       </c>
-      <c r="C16" s="244"/>
+      <c r="C16" s="245"/>
     </row>
     <row r="17" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B17" s="249" t="s">
+      <c r="B17" s="250" t="s">
         <v>408</v>
       </c>
-      <c r="C17" s="244"/>
+      <c r="C17" s="245"/>
     </row>
     <row r="18" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="250" t="s">
         <v>409</v>
       </c>
-      <c r="C18" s="244"/>
+      <c r="C18" s="245"/>
     </row>
     <row r="19" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B19" s="249" t="s">
+      <c r="B19" s="250" t="s">
         <v>410</v>
       </c>
-      <c r="C19" s="244"/>
+      <c r="C19" s="245"/>
     </row>
     <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="252" t="s">
+      <c r="B20" s="254" t="s">
         <v>411</v>
       </c>
-      <c r="C20" s="244"/>
+      <c r="C20" s="245"/>
     </row>
     <row r="21" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B21" s="251" t="s">
+      <c r="B21" s="249" t="s">
         <v>412</v>
       </c>
-      <c r="C21" s="244"/>
+      <c r="C21" s="245"/>
     </row>
     <row r="22" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B22" s="251" t="s">
+      <c r="B22" s="249" t="s">
         <v>413</v>
       </c>
-      <c r="C22" s="244"/>
+      <c r="C22" s="245"/>
     </row>
     <row r="23" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B23" s="251" t="s">
+      <c r="B23" s="249" t="s">
         <v>414</v>
       </c>
-      <c r="C23" s="244"/>
+      <c r="C23" s="245"/>
     </row>
     <row r="24" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B24" s="251" t="s">
+      <c r="B24" s="249" t="s">
         <v>415</v>
       </c>
-      <c r="C24" s="244"/>
+      <c r="C24" s="245"/>
     </row>
     <row r="25" spans="2:3" ht="6" customHeight="1"/>
     <row r="26" spans="2:3" ht="18" customHeight="1">
-      <c r="B26" s="247" t="s">
+      <c r="B26" s="251" t="s">
         <v>416</v>
       </c>
-      <c r="C26" s="244"/>
+      <c r="C26" s="245"/>
     </row>
     <row r="27" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B27" s="250" t="s">
+      <c r="B27" s="248" t="s">
         <v>399</v>
       </c>
-      <c r="C27" s="244"/>
+      <c r="C27" s="245"/>
     </row>
     <row r="28" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B28" s="249" t="s">
+      <c r="B28" s="250" t="s">
         <v>417</v>
       </c>
-      <c r="C28" s="244"/>
+      <c r="C28" s="245"/>
     </row>
     <row r="29" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="250" t="s">
         <v>418</v>
       </c>
-      <c r="C29" s="244"/>
+      <c r="C29" s="245"/>
     </row>
     <row r="30" spans="2:3" ht="14.1" customHeight="1">
       <c r="B30" s="159"/>
@@ -7462,86 +7468,86 @@
       <c r="B46" s="159"/>
     </row>
     <row r="47" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B47" s="250" t="s">
+      <c r="B47" s="248" t="s">
         <v>419</v>
       </c>
-      <c r="C47" s="244"/>
+      <c r="C47" s="245"/>
     </row>
     <row r="48" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B48" s="249" t="s">
+      <c r="B48" s="250" t="s">
         <v>420</v>
       </c>
-      <c r="C48" s="244"/>
+      <c r="C48" s="245"/>
     </row>
     <row r="49" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B49" s="249" t="s">
+      <c r="B49" s="250" t="s">
         <v>421</v>
       </c>
-      <c r="C49" s="244"/>
+      <c r="C49" s="245"/>
     </row>
     <row r="50" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B50" s="250" t="s">
+      <c r="B50" s="248" t="s">
         <v>406</v>
       </c>
-      <c r="C50" s="244"/>
+      <c r="C50" s="245"/>
     </row>
     <row r="51" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B51" s="249" t="s">
+      <c r="B51" s="250" t="s">
         <v>422</v>
       </c>
-      <c r="C51" s="244"/>
+      <c r="C51" s="245"/>
     </row>
     <row r="52" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="250" t="s">
         <v>423</v>
       </c>
-      <c r="C52" s="244"/>
+      <c r="C52" s="245"/>
     </row>
     <row r="53" spans="2:3" ht="6" customHeight="1"/>
     <row r="54" spans="2:3" ht="18" customHeight="1">
-      <c r="B54" s="247" t="s">
+      <c r="B54" s="251" t="s">
         <v>424</v>
       </c>
-      <c r="C54" s="244"/>
+      <c r="C54" s="245"/>
     </row>
     <row r="55" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B55" s="250" t="s">
+      <c r="B55" s="248" t="s">
         <v>425</v>
       </c>
-      <c r="C55" s="244"/>
+      <c r="C55" s="245"/>
     </row>
     <row r="56" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B56" s="249" t="s">
+      <c r="B56" s="250" t="s">
         <v>426</v>
       </c>
-      <c r="C56" s="244"/>
+      <c r="C56" s="245"/>
     </row>
     <row r="57" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B57" s="248" t="s">
+      <c r="B57" s="253" t="s">
         <v>427</v>
       </c>
-      <c r="C57" s="244"/>
+      <c r="C57" s="245"/>
     </row>
     <row r="58" spans="2:3" ht="14.1" customHeight="1">
       <c r="B58" s="161"/>
     </row>
     <row r="59" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B59" s="250" t="s">
+      <c r="B59" s="248" t="s">
         <v>428</v>
       </c>
-      <c r="C59" s="244"/>
+      <c r="C59" s="245"/>
     </row>
     <row r="60" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B60" s="249" t="s">
+      <c r="B60" s="250" t="s">
         <v>429</v>
       </c>
-      <c r="C60" s="244"/>
+      <c r="C60" s="245"/>
     </row>
     <row r="61" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B61" s="249" t="s">
+      <c r="B61" s="250" t="s">
         <v>430</v>
       </c>
-      <c r="C61" s="244"/>
+      <c r="C61" s="245"/>
     </row>
     <row r="62" spans="2:3" ht="14.1" customHeight="1">
       <c r="B62" s="159"/>
@@ -7604,42 +7610,42 @@
       <c r="B80" s="159"/>
     </row>
     <row r="81" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B81" s="250" t="s">
+      <c r="B81" s="248" t="s">
         <v>404</v>
       </c>
-      <c r="C81" s="244"/>
+      <c r="C81" s="245"/>
     </row>
     <row r="82" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B82" s="249" t="s">
+      <c r="B82" s="250" t="s">
         <v>432</v>
       </c>
-      <c r="C82" s="244"/>
+      <c r="C82" s="245"/>
     </row>
     <row r="83" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B83" s="250" t="s">
+      <c r="B83" s="248" t="s">
         <v>406</v>
       </c>
-      <c r="C83" s="244"/>
+      <c r="C83" s="245"/>
     </row>
     <row r="84" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B84" s="249" t="s">
+      <c r="B84" s="250" t="s">
         <v>433</v>
       </c>
-      <c r="C84" s="244"/>
+      <c r="C84" s="245"/>
     </row>
     <row r="85" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B85" s="249" t="s">
+      <c r="B85" s="250" t="s">
         <v>434</v>
       </c>
-      <c r="C85" s="244"/>
+      <c r="C85" s="245"/>
     </row>
     <row r="86" spans="2:3" ht="6" customHeight="1"/>
     <row r="87" spans="2:3" ht="6" customHeight="1"/>
     <row r="88" spans="2:3" ht="18" customHeight="1">
-      <c r="B88" s="247" t="s">
+      <c r="B88" s="251" t="s">
         <v>435</v>
       </c>
-      <c r="C88" s="244"/>
+      <c r="C88" s="245"/>
     </row>
     <row r="89" spans="2:3" ht="15.95" customHeight="1">
       <c r="B89" s="147" t="s">
@@ -7685,30 +7691,6 @@
     <row r="95" spans="2:3" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B88:C88"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B82:C82"/>
@@ -7725,6 +7707,30 @@
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B59:C59"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7747,29 +7753,29 @@
   <sheetData>
     <row r="1" spans="2:5" ht="6" customHeight="1"/>
     <row r="2" spans="2:5" ht="24" customHeight="1">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="261" t="s">
         <v>440</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
     </row>
     <row r="3" spans="2:5" ht="6" customHeight="1"/>
     <row r="4" spans="2:5" ht="18" customHeight="1">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="259" t="s">
         <v>441</v>
       </c>
-      <c r="C4" s="244"/>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
     </row>
     <row r="5" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B5" s="257" t="s">
+      <c r="B5" s="258" t="s">
         <v>442</v>
       </c>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
     </row>
     <row r="6" spans="2:5" ht="3.95" customHeight="1"/>
     <row r="7" spans="2:5" ht="15.95" customHeight="1">
@@ -7928,320 +7934,320 @@
     </row>
     <row r="18" spans="2:5" ht="6" customHeight="1"/>
     <row r="19" spans="2:5" ht="18" customHeight="1">
-      <c r="B19" s="254" t="s">
+      <c r="B19" s="259" t="s">
         <v>474</v>
       </c>
-      <c r="C19" s="244"/>
-      <c r="D19" s="244"/>
-      <c r="E19" s="244"/>
+      <c r="C19" s="245"/>
+      <c r="D19" s="245"/>
+      <c r="E19" s="245"/>
     </row>
     <row r="20" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B20" s="255" t="s">
+      <c r="B20" s="260" t="s">
         <v>475</v>
       </c>
-      <c r="C20" s="244"/>
-      <c r="D20" s="244"/>
-      <c r="E20" s="244"/>
+      <c r="C20" s="245"/>
+      <c r="D20" s="245"/>
+      <c r="E20" s="245"/>
     </row>
     <row r="21" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B21" s="259" t="s">
+      <c r="B21" s="256" t="s">
         <v>476</v>
       </c>
-      <c r="C21" s="244"/>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
+      <c r="C21" s="245"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
     </row>
     <row r="22" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B22" s="256" t="s">
+      <c r="B22" s="255" t="s">
         <v>477</v>
       </c>
-      <c r="C22" s="244"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
+      <c r="C22" s="245"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
     </row>
     <row r="23" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B23" s="256" t="s">
+      <c r="B23" s="255" t="s">
         <v>478</v>
       </c>
-      <c r="C23" s="244"/>
-      <c r="D23" s="244"/>
-      <c r="E23" s="244"/>
+      <c r="C23" s="245"/>
+      <c r="D23" s="245"/>
+      <c r="E23" s="245"/>
     </row>
     <row r="24" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B24" s="256" t="s">
+      <c r="B24" s="255" t="s">
         <v>479</v>
       </c>
-      <c r="C24" s="244"/>
-      <c r="D24" s="244"/>
-      <c r="E24" s="244"/>
+      <c r="C24" s="245"/>
+      <c r="D24" s="245"/>
+      <c r="E24" s="245"/>
     </row>
     <row r="25" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B25" s="256" t="s">
+      <c r="B25" s="255" t="s">
         <v>480</v>
       </c>
-      <c r="C25" s="244"/>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
+      <c r="C25" s="245"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="245"/>
     </row>
     <row r="26" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B26" s="256" t="s">
+      <c r="B26" s="255" t="s">
         <v>481</v>
       </c>
-      <c r="C26" s="244"/>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
+      <c r="C26" s="245"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
     </row>
     <row r="27" spans="2:5" ht="6" customHeight="1"/>
     <row r="28" spans="2:5" ht="18" customHeight="1">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="259" t="s">
         <v>482</v>
       </c>
-      <c r="C28" s="244"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="244"/>
+      <c r="C28" s="245"/>
+      <c r="D28" s="245"/>
+      <c r="E28" s="245"/>
     </row>
     <row r="29" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B29" s="255" t="s">
+      <c r="B29" s="260" t="s">
         <v>483</v>
       </c>
-      <c r="C29" s="244"/>
-      <c r="D29" s="244"/>
-      <c r="E29" s="244"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
     </row>
     <row r="30" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B30" s="259" t="s">
+      <c r="B30" s="256" t="s">
         <v>476</v>
       </c>
-      <c r="C30" s="244"/>
-      <c r="D30" s="244"/>
-      <c r="E30" s="244"/>
+      <c r="C30" s="245"/>
+      <c r="D30" s="245"/>
+      <c r="E30" s="245"/>
     </row>
     <row r="31" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B31" s="256" t="s">
+      <c r="B31" s="255" t="s">
         <v>484</v>
       </c>
-      <c r="C31" s="244"/>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
+      <c r="C31" s="245"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
     </row>
     <row r="32" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B32" s="256" t="s">
+      <c r="B32" s="255" t="s">
         <v>485</v>
       </c>
-      <c r="C32" s="244"/>
-      <c r="D32" s="244"/>
-      <c r="E32" s="244"/>
+      <c r="C32" s="245"/>
+      <c r="D32" s="245"/>
+      <c r="E32" s="245"/>
     </row>
     <row r="33" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B33" s="256" t="s">
+      <c r="B33" s="255" t="s">
         <v>486</v>
       </c>
-      <c r="C33" s="244"/>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
+      <c r="C33" s="245"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
     </row>
     <row r="34" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B34" s="256" t="s">
+      <c r="B34" s="255" t="s">
         <v>487</v>
       </c>
-      <c r="C34" s="244"/>
-      <c r="D34" s="244"/>
-      <c r="E34" s="244"/>
+      <c r="C34" s="245"/>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
     </row>
     <row r="35" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B35" s="256" t="s">
+      <c r="B35" s="255" t="s">
         <v>481</v>
       </c>
-      <c r="C35" s="244"/>
-      <c r="D35" s="244"/>
-      <c r="E35" s="244"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
     </row>
     <row r="36" spans="2:5" ht="6" customHeight="1"/>
     <row r="37" spans="2:5" ht="18" customHeight="1">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="259" t="s">
         <v>488</v>
       </c>
-      <c r="C37" s="244"/>
-      <c r="D37" s="244"/>
-      <c r="E37" s="244"/>
+      <c r="C37" s="245"/>
+      <c r="D37" s="245"/>
+      <c r="E37" s="245"/>
     </row>
     <row r="38" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B38" s="260" t="s">
+      <c r="B38" s="257" t="s">
         <v>489</v>
       </c>
-      <c r="C38" s="244"/>
-      <c r="D38" s="244"/>
-      <c r="E38" s="244"/>
+      <c r="C38" s="245"/>
+      <c r="D38" s="245"/>
+      <c r="E38" s="245"/>
     </row>
     <row r="39" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B39" s="259" t="s">
+      <c r="B39" s="256" t="s">
         <v>490</v>
       </c>
-      <c r="C39" s="244"/>
-      <c r="D39" s="244"/>
-      <c r="E39" s="244"/>
+      <c r="C39" s="245"/>
+      <c r="D39" s="245"/>
+      <c r="E39" s="245"/>
     </row>
     <row r="40" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B40" s="256" t="s">
+      <c r="B40" s="255" t="s">
         <v>491</v>
       </c>
-      <c r="C40" s="244"/>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
+      <c r="C40" s="245"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
     </row>
     <row r="41" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B41" s="256" t="s">
+      <c r="B41" s="255" t="s">
         <v>492</v>
       </c>
-      <c r="C41" s="244"/>
-      <c r="D41" s="244"/>
-      <c r="E41" s="244"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="245"/>
+      <c r="E41" s="245"/>
     </row>
     <row r="42" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B42" s="256" t="s">
+      <c r="B42" s="255" t="s">
         <v>493</v>
       </c>
-      <c r="C42" s="244"/>
-      <c r="D42" s="244"/>
-      <c r="E42" s="244"/>
+      <c r="C42" s="245"/>
+      <c r="D42" s="245"/>
+      <c r="E42" s="245"/>
     </row>
     <row r="43" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B43" s="256" t="s">
+      <c r="B43" s="255" t="s">
         <v>494</v>
       </c>
-      <c r="C43" s="244"/>
-      <c r="D43" s="244"/>
-      <c r="E43" s="244"/>
+      <c r="C43" s="245"/>
+      <c r="D43" s="245"/>
+      <c r="E43" s="245"/>
     </row>
     <row r="44" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B44" s="256" t="s">
+      <c r="B44" s="255" t="s">
         <v>495</v>
       </c>
-      <c r="C44" s="244"/>
-      <c r="D44" s="244"/>
-      <c r="E44" s="244"/>
+      <c r="C44" s="245"/>
+      <c r="D44" s="245"/>
+      <c r="E44" s="245"/>
     </row>
     <row r="45" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B45" s="257" t="s">
+      <c r="B45" s="258" t="s">
         <v>496</v>
       </c>
-      <c r="C45" s="244"/>
-      <c r="D45" s="244"/>
-      <c r="E45" s="244"/>
+      <c r="C45" s="245"/>
+      <c r="D45" s="245"/>
+      <c r="E45" s="245"/>
     </row>
     <row r="46" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B46" s="257" t="s">
+      <c r="B46" s="258" t="s">
         <v>497</v>
       </c>
-      <c r="C46" s="244"/>
-      <c r="D46" s="244"/>
-      <c r="E46" s="244"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
     </row>
     <row r="47" spans="2:5" ht="6" customHeight="1"/>
     <row r="48" spans="2:5" ht="18" customHeight="1">
-      <c r="B48" s="254" t="s">
+      <c r="B48" s="259" t="s">
         <v>498</v>
       </c>
-      <c r="C48" s="244"/>
-      <c r="D48" s="244"/>
-      <c r="E48" s="244"/>
+      <c r="C48" s="245"/>
+      <c r="D48" s="245"/>
+      <c r="E48" s="245"/>
     </row>
     <row r="49" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B49" s="260" t="s">
+      <c r="B49" s="257" t="s">
         <v>499</v>
       </c>
-      <c r="C49" s="244"/>
-      <c r="D49" s="244"/>
-      <c r="E49" s="244"/>
+      <c r="C49" s="245"/>
+      <c r="D49" s="245"/>
+      <c r="E49" s="245"/>
     </row>
     <row r="50" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B50" s="259" t="s">
+      <c r="B50" s="256" t="s">
         <v>490</v>
       </c>
-      <c r="C50" s="244"/>
-      <c r="D50" s="244"/>
-      <c r="E50" s="244"/>
+      <c r="C50" s="245"/>
+      <c r="D50" s="245"/>
+      <c r="E50" s="245"/>
     </row>
     <row r="51" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B51" s="256" t="s">
+      <c r="B51" s="255" t="s">
         <v>491</v>
       </c>
-      <c r="C51" s="244"/>
-      <c r="D51" s="244"/>
-      <c r="E51" s="244"/>
+      <c r="C51" s="245"/>
+      <c r="D51" s="245"/>
+      <c r="E51" s="245"/>
     </row>
     <row r="52" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B52" s="256" t="s">
+      <c r="B52" s="255" t="s">
         <v>500</v>
       </c>
-      <c r="C52" s="244"/>
-      <c r="D52" s="244"/>
-      <c r="E52" s="244"/>
+      <c r="C52" s="245"/>
+      <c r="D52" s="245"/>
+      <c r="E52" s="245"/>
     </row>
     <row r="53" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B53" s="256" t="s">
+      <c r="B53" s="255" t="s">
         <v>493</v>
       </c>
-      <c r="C53" s="244"/>
-      <c r="D53" s="244"/>
-      <c r="E53" s="244"/>
+      <c r="C53" s="245"/>
+      <c r="D53" s="245"/>
+      <c r="E53" s="245"/>
     </row>
     <row r="54" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B54" s="256" t="s">
+      <c r="B54" s="255" t="s">
         <v>494</v>
       </c>
-      <c r="C54" s="244"/>
-      <c r="D54" s="244"/>
-      <c r="E54" s="244"/>
+      <c r="C54" s="245"/>
+      <c r="D54" s="245"/>
+      <c r="E54" s="245"/>
     </row>
     <row r="55" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B55" s="256" t="s">
+      <c r="B55" s="255" t="s">
         <v>501</v>
       </c>
-      <c r="C55" s="244"/>
-      <c r="D55" s="244"/>
-      <c r="E55" s="244"/>
+      <c r="C55" s="245"/>
+      <c r="D55" s="245"/>
+      <c r="E55" s="245"/>
     </row>
     <row r="56" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B56" s="257" t="s">
+      <c r="B56" s="258" t="s">
         <v>502</v>
       </c>
-      <c r="C56" s="244"/>
-      <c r="D56" s="244"/>
-      <c r="E56" s="244"/>
+      <c r="C56" s="245"/>
+      <c r="D56" s="245"/>
+      <c r="E56" s="245"/>
     </row>
     <row r="57" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B57" s="257" t="s">
+      <c r="B57" s="258" t="s">
         <v>497</v>
       </c>
-      <c r="C57" s="244"/>
-      <c r="D57" s="244"/>
-      <c r="E57" s="244"/>
+      <c r="C57" s="245"/>
+      <c r="D57" s="245"/>
+      <c r="E57" s="245"/>
     </row>
     <row r="58" spans="2:5" ht="6" customHeight="1"/>
     <row r="59" spans="2:5" ht="18" customHeight="1">
-      <c r="B59" s="254" t="s">
+      <c r="B59" s="259" t="s">
         <v>503</v>
       </c>
-      <c r="C59" s="244"/>
-      <c r="D59" s="244"/>
-      <c r="E59" s="244"/>
+      <c r="C59" s="245"/>
+      <c r="D59" s="245"/>
+      <c r="E59" s="245"/>
     </row>
     <row r="60" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B60" s="255" t="s">
+      <c r="B60" s="260" t="s">
         <v>504</v>
       </c>
-      <c r="C60" s="244"/>
-      <c r="D60" s="244"/>
-      <c r="E60" s="244"/>
+      <c r="C60" s="245"/>
+      <c r="D60" s="245"/>
+      <c r="E60" s="245"/>
     </row>
     <row r="61" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B61" s="257" t="s">
+      <c r="B61" s="258" t="s">
         <v>505</v>
       </c>
-      <c r="C61" s="244"/>
-      <c r="D61" s="244"/>
-      <c r="E61" s="244"/>
+      <c r="C61" s="245"/>
+      <c r="D61" s="245"/>
+      <c r="E61" s="245"/>
     </row>
     <row r="62" spans="2:5" ht="3.95" customHeight="1"/>
     <row r="63" spans="2:5" ht="15.95" customHeight="1">
@@ -8652,175 +8658,175 @@
     </row>
     <row r="92" spans="2:5" ht="6" customHeight="1"/>
     <row r="93" spans="2:5" ht="18" customHeight="1">
-      <c r="B93" s="254" t="s">
+      <c r="B93" s="259" t="s">
         <v>519</v>
       </c>
-      <c r="C93" s="244"/>
-      <c r="D93" s="244"/>
-      <c r="E93" s="244"/>
+      <c r="C93" s="245"/>
+      <c r="D93" s="245"/>
+      <c r="E93" s="245"/>
     </row>
     <row r="94" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B94" s="255" t="s">
+      <c r="B94" s="260" t="s">
         <v>520</v>
       </c>
-      <c r="C94" s="244"/>
-      <c r="D94" s="244"/>
-      <c r="E94" s="244"/>
+      <c r="C94" s="245"/>
+      <c r="D94" s="245"/>
+      <c r="E94" s="245"/>
     </row>
     <row r="95" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B95" s="259" t="s">
+      <c r="B95" s="256" t="s">
         <v>521</v>
       </c>
-      <c r="C95" s="244"/>
-      <c r="D95" s="244"/>
-      <c r="E95" s="244"/>
+      <c r="C95" s="245"/>
+      <c r="D95" s="245"/>
+      <c r="E95" s="245"/>
     </row>
     <row r="96" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B96" s="256" t="s">
+      <c r="B96" s="255" t="s">
         <v>522</v>
       </c>
-      <c r="C96" s="244"/>
-      <c r="D96" s="244"/>
-      <c r="E96" s="244"/>
+      <c r="C96" s="245"/>
+      <c r="D96" s="245"/>
+      <c r="E96" s="245"/>
     </row>
     <row r="97" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B97" s="256" t="s">
+      <c r="B97" s="255" t="s">
         <v>523</v>
       </c>
-      <c r="C97" s="244"/>
-      <c r="D97" s="244"/>
-      <c r="E97" s="244"/>
+      <c r="C97" s="245"/>
+      <c r="D97" s="245"/>
+      <c r="E97" s="245"/>
     </row>
     <row r="98" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B98" s="256" t="s">
+      <c r="B98" s="255" t="s">
         <v>493</v>
       </c>
-      <c r="C98" s="244"/>
-      <c r="D98" s="244"/>
-      <c r="E98" s="244"/>
+      <c r="C98" s="245"/>
+      <c r="D98" s="245"/>
+      <c r="E98" s="245"/>
     </row>
     <row r="99" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B99" s="256" t="s">
+      <c r="B99" s="255" t="s">
         <v>494</v>
       </c>
-      <c r="C99" s="244"/>
-      <c r="D99" s="244"/>
-      <c r="E99" s="244"/>
+      <c r="C99" s="245"/>
+      <c r="D99" s="245"/>
+      <c r="E99" s="245"/>
     </row>
     <row r="100" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B100" s="256" t="s">
+      <c r="B100" s="255" t="s">
         <v>524</v>
       </c>
-      <c r="C100" s="244"/>
-      <c r="D100" s="244"/>
-      <c r="E100" s="244"/>
+      <c r="C100" s="245"/>
+      <c r="D100" s="245"/>
+      <c r="E100" s="245"/>
     </row>
     <row r="101" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B101" s="259" t="s">
+      <c r="B101" s="256" t="s">
         <v>525</v>
       </c>
-      <c r="C101" s="244"/>
-      <c r="D101" s="244"/>
-      <c r="E101" s="244"/>
+      <c r="C101" s="245"/>
+      <c r="D101" s="245"/>
+      <c r="E101" s="245"/>
     </row>
     <row r="102" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B102" s="257" t="s">
+      <c r="B102" s="258" t="s">
         <v>526</v>
       </c>
-      <c r="C102" s="244"/>
-      <c r="D102" s="244"/>
-      <c r="E102" s="244"/>
+      <c r="C102" s="245"/>
+      <c r="D102" s="245"/>
+      <c r="E102" s="245"/>
     </row>
     <row r="103" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B103" s="257" t="s">
+      <c r="B103" s="258" t="s">
         <v>527</v>
       </c>
-      <c r="C103" s="244"/>
-      <c r="D103" s="244"/>
-      <c r="E103" s="244"/>
+      <c r="C103" s="245"/>
+      <c r="D103" s="245"/>
+      <c r="E103" s="245"/>
     </row>
     <row r="104" spans="2:5" ht="6" customHeight="1"/>
     <row r="105" spans="2:5" ht="18" customHeight="1">
-      <c r="B105" s="254" t="s">
+      <c r="B105" s="259" t="s">
         <v>528</v>
       </c>
-      <c r="C105" s="244"/>
-      <c r="D105" s="244"/>
-      <c r="E105" s="244"/>
+      <c r="C105" s="245"/>
+      <c r="D105" s="245"/>
+      <c r="E105" s="245"/>
     </row>
     <row r="106" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B106" s="255" t="s">
+      <c r="B106" s="260" t="s">
         <v>529</v>
       </c>
-      <c r="C106" s="244"/>
-      <c r="D106" s="244"/>
-      <c r="E106" s="244"/>
+      <c r="C106" s="245"/>
+      <c r="D106" s="245"/>
+      <c r="E106" s="245"/>
     </row>
     <row r="107" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B107" s="257" t="s">
+      <c r="B107" s="258" t="s">
         <v>530</v>
       </c>
-      <c r="C107" s="244"/>
-      <c r="D107" s="244"/>
-      <c r="E107" s="244"/>
+      <c r="C107" s="245"/>
+      <c r="D107" s="245"/>
+      <c r="E107" s="245"/>
     </row>
     <row r="108" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B108" s="259" t="s">
+      <c r="B108" s="256" t="s">
         <v>490</v>
       </c>
-      <c r="C108" s="244"/>
-      <c r="D108" s="244"/>
-      <c r="E108" s="244"/>
+      <c r="C108" s="245"/>
+      <c r="D108" s="245"/>
+      <c r="E108" s="245"/>
     </row>
     <row r="109" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B109" s="256" t="s">
+      <c r="B109" s="255" t="s">
         <v>491</v>
       </c>
-      <c r="C109" s="244"/>
-      <c r="D109" s="244"/>
-      <c r="E109" s="244"/>
+      <c r="C109" s="245"/>
+      <c r="D109" s="245"/>
+      <c r="E109" s="245"/>
     </row>
     <row r="110" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B110" s="256" t="s">
+      <c r="B110" s="255" t="s">
         <v>531</v>
       </c>
-      <c r="C110" s="244"/>
-      <c r="D110" s="244"/>
-      <c r="E110" s="244"/>
+      <c r="C110" s="245"/>
+      <c r="D110" s="245"/>
+      <c r="E110" s="245"/>
     </row>
     <row r="111" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B111" s="256" t="s">
+      <c r="B111" s="255" t="s">
         <v>493</v>
       </c>
-      <c r="C111" s="244"/>
-      <c r="D111" s="244"/>
-      <c r="E111" s="244"/>
+      <c r="C111" s="245"/>
+      <c r="D111" s="245"/>
+      <c r="E111" s="245"/>
     </row>
     <row r="112" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B112" s="256" t="s">
+      <c r="B112" s="255" t="s">
         <v>494</v>
       </c>
-      <c r="C112" s="244"/>
-      <c r="D112" s="244"/>
-      <c r="E112" s="244"/>
+      <c r="C112" s="245"/>
+      <c r="D112" s="245"/>
+      <c r="E112" s="245"/>
     </row>
     <row r="113" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B113" s="256" t="s">
+      <c r="B113" s="255" t="s">
         <v>532</v>
       </c>
-      <c r="C113" s="244"/>
-      <c r="D113" s="244"/>
-      <c r="E113" s="244"/>
+      <c r="C113" s="245"/>
+      <c r="D113" s="245"/>
+      <c r="E113" s="245"/>
     </row>
     <row r="114" spans="2:5" ht="6" customHeight="1"/>
     <row r="115" spans="2:5" ht="6" customHeight="1"/>
     <row r="116" spans="2:5" ht="18" customHeight="1">
-      <c r="B116" s="254" t="s">
+      <c r="B116" s="259" t="s">
         <v>533</v>
       </c>
-      <c r="C116" s="244"/>
-      <c r="D116" s="244"/>
-      <c r="E116" s="244"/>
+      <c r="C116" s="245"/>
+      <c r="D116" s="245"/>
+      <c r="E116" s="245"/>
     </row>
     <row r="117" spans="2:5" ht="3.95" customHeight="1"/>
     <row r="118" spans="2:5" ht="15.95" customHeight="1">
@@ -8952,21 +8958,38 @@
     <row r="127" spans="2:5" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B112:E112"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B113:E113"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B100:E100"/>
     <mergeCell ref="B110:E110"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B4:E4"/>
@@ -8983,38 +9006,21 @@
     <mergeCell ref="B95:E95"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B113:E113"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B45:E45"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9037,32 +9043,32 @@
   <sheetData>
     <row r="1" spans="2:14" ht="6" customHeight="1"/>
     <row r="2" spans="2:14" ht="24" customHeight="1">
-      <c r="B2" s="258" t="s">
-        <v>708</v>
-      </c>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
+      <c r="B2" s="261" t="s">
+        <v>706</v>
+      </c>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
     </row>
     <row r="3" spans="2:14" ht="6" customHeight="1"/>
     <row r="4" spans="2:14" ht="18" customHeight="1">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="259" t="s">
         <v>557</v>
       </c>
-      <c r="C4" s="244"/>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
     </row>
     <row r="5" spans="2:14" ht="14.1" customHeight="1">
-      <c r="B5" s="262" t="s">
-        <v>712</v>
-      </c>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
+      <c r="B5" s="268" t="s">
+        <v>710</v>
+      </c>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
     </row>
     <row r="6" spans="2:14" ht="3.95" customHeight="1"/>
     <row r="7" spans="2:14" ht="15.95" customHeight="1">
@@ -9087,7 +9093,7 @@
         <v>563</v>
       </c>
       <c r="D8" s="173" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E8" s="164" t="s">
         <v>564</v>
@@ -9174,7 +9180,7 @@
         <v>574</v>
       </c>
       <c r="E12" s="171" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H12" s="160"/>
       <c r="I12" s="160"/>
@@ -9194,13 +9200,13 @@
       <c r="N13" s="160"/>
     </row>
     <row r="14" spans="2:14" ht="18" customHeight="1">
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="259" t="s">
         <v>575</v>
       </c>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
       <c r="H14" s="78"/>
       <c r="I14" s="160"/>
       <c r="J14" s="160"/>
@@ -9210,13 +9216,13 @@
       <c r="N14" s="160"/>
     </row>
     <row r="15" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="256" t="s">
         <v>576</v>
       </c>
-      <c r="C15" s="244"/>
-      <c r="D15" s="244"/>
-      <c r="E15" s="244"/>
-      <c r="F15" s="244"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
       <c r="H15" s="160"/>
       <c r="I15" s="160"/>
       <c r="J15" s="160"/>
@@ -9226,13 +9232,13 @@
       <c r="N15" s="160"/>
     </row>
     <row r="16" spans="2:14" ht="14.1" customHeight="1">
-      <c r="B16" s="257" t="s">
+      <c r="B16" s="258" t="s">
         <v>577</v>
       </c>
-      <c r="C16" s="244"/>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
+      <c r="C16" s="245"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="245"/>
       <c r="H16" s="160"/>
       <c r="I16" s="160"/>
       <c r="J16" s="160"/>
@@ -9242,13 +9248,13 @@
       <c r="N16" s="160"/>
     </row>
     <row r="17" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B17" s="263" t="s">
-        <v>718</v>
-      </c>
-      <c r="C17" s="244"/>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
+      <c r="B17" s="262" t="s">
+        <v>716</v>
+      </c>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
       <c r="H17" s="160"/>
       <c r="I17" s="160"/>
       <c r="J17" s="160"/>
@@ -9258,13 +9264,13 @@
       <c r="N17" s="160"/>
     </row>
     <row r="18" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B18" s="263" t="s">
-        <v>713</v>
-      </c>
-      <c r="C18" s="244"/>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
+      <c r="B18" s="262" t="s">
+        <v>711</v>
+      </c>
+      <c r="C18" s="245"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
       <c r="H18" s="160"/>
       <c r="I18" s="160"/>
       <c r="J18" s="160"/>
@@ -9274,203 +9280,203 @@
       <c r="N18" s="160"/>
     </row>
     <row r="19" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B19" s="263" t="s">
+      <c r="B19" s="262" t="s">
+        <v>712</v>
+      </c>
+      <c r="C19" s="245"/>
+      <c r="D19" s="245"/>
+      <c r="E19" s="245"/>
+      <c r="F19" s="245"/>
+    </row>
+    <row r="20" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B20" s="255" t="s">
+        <v>578</v>
+      </c>
+      <c r="C20" s="245"/>
+      <c r="D20" s="245"/>
+      <c r="E20" s="245"/>
+      <c r="F20" s="245"/>
+    </row>
+    <row r="21" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B21" s="262" t="s">
+        <v>713</v>
+      </c>
+      <c r="C21" s="245"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="245"/>
+    </row>
+    <row r="22" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B22" s="262" t="s">
+        <v>715</v>
+      </c>
+      <c r="C22" s="245"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+    </row>
+    <row r="23" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B23" s="262" t="s">
         <v>714</v>
       </c>
-      <c r="C19" s="244"/>
-      <c r="D19" s="244"/>
-      <c r="E19" s="244"/>
-      <c r="F19" s="244"/>
-    </row>
-    <row r="20" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B20" s="256" t="s">
-        <v>578</v>
-      </c>
-      <c r="C20" s="244"/>
-      <c r="D20" s="244"/>
-      <c r="E20" s="244"/>
-      <c r="F20" s="244"/>
-    </row>
-    <row r="21" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B21" s="263" t="s">
-        <v>715</v>
-      </c>
-      <c r="C21" s="244"/>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-    </row>
-    <row r="22" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B22" s="263" t="s">
+      <c r="C23" s="245"/>
+      <c r="D23" s="245"/>
+      <c r="E23" s="245"/>
+      <c r="F23" s="245"/>
+    </row>
+    <row r="24" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B24" s="255" t="s">
+        <v>579</v>
+      </c>
+      <c r="C24" s="245"/>
+      <c r="D24" s="245"/>
+      <c r="E24" s="245"/>
+      <c r="F24" s="245"/>
+    </row>
+    <row r="25" spans="2:14" ht="15.95" customHeight="1">
+      <c r="B25" s="256" t="s">
+        <v>580</v>
+      </c>
+      <c r="C25" s="245"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+    </row>
+    <row r="26" spans="2:14" ht="14.1" customHeight="1">
+      <c r="B26" s="258" t="s">
+        <v>581</v>
+      </c>
+      <c r="C26" s="245"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+    </row>
+    <row r="27" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B27" s="255" t="s">
+        <v>582</v>
+      </c>
+      <c r="C27" s="245"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+    </row>
+    <row r="28" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B28" s="255" t="s">
+        <v>583</v>
+      </c>
+      <c r="C28" s="245"/>
+      <c r="D28" s="245"/>
+      <c r="E28" s="245"/>
+      <c r="F28" s="245"/>
+    </row>
+    <row r="29" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B29" s="255" t="s">
+        <v>584</v>
+      </c>
+      <c r="C29" s="245"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+    </row>
+    <row r="30" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B30" s="255" t="s">
+        <v>585</v>
+      </c>
+      <c r="C30" s="245"/>
+      <c r="D30" s="245"/>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+    </row>
+    <row r="31" spans="2:14" ht="12.95" customHeight="1">
+      <c r="B31" s="255" t="s">
+        <v>586</v>
+      </c>
+      <c r="C31" s="245"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+    </row>
+    <row r="32" spans="2:14" ht="15.95" customHeight="1">
+      <c r="B32" s="256" t="s">
+        <v>587</v>
+      </c>
+      <c r="C32" s="245"/>
+      <c r="D32" s="245"/>
+      <c r="E32" s="245"/>
+      <c r="F32" s="245"/>
+    </row>
+    <row r="33" spans="2:6" ht="14.1" customHeight="1">
+      <c r="B33" s="258" t="s">
+        <v>588</v>
+      </c>
+      <c r="C33" s="245"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+    </row>
+    <row r="34" spans="2:6" ht="12.95" customHeight="1">
+      <c r="B34" s="255" t="s">
+        <v>589</v>
+      </c>
+      <c r="C34" s="245"/>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="245"/>
+    </row>
+    <row r="35" spans="2:6" ht="12.95" customHeight="1">
+      <c r="B35" s="263" t="s">
         <v>717</v>
       </c>
-      <c r="C22" s="244"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-    </row>
-    <row r="23" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B23" s="263" t="s">
-        <v>716</v>
-      </c>
-      <c r="C23" s="244"/>
-      <c r="D23" s="244"/>
-      <c r="E23" s="244"/>
-      <c r="F23" s="244"/>
-    </row>
-    <row r="24" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B24" s="256" t="s">
-        <v>579</v>
-      </c>
-      <c r="C24" s="244"/>
-      <c r="D24" s="244"/>
-      <c r="E24" s="244"/>
-      <c r="F24" s="244"/>
-    </row>
-    <row r="25" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B25" s="259" t="s">
-        <v>580</v>
-      </c>
-      <c r="C25" s="244"/>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-    </row>
-    <row r="26" spans="2:14" ht="14.1" customHeight="1">
-      <c r="B26" s="257" t="s">
-        <v>581</v>
-      </c>
-      <c r="C26" s="244"/>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-    </row>
-    <row r="27" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B27" s="256" t="s">
-        <v>582</v>
-      </c>
-      <c r="C27" s="244"/>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
-      <c r="F27" s="244"/>
-    </row>
-    <row r="28" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B28" s="256" t="s">
-        <v>583</v>
-      </c>
-      <c r="C28" s="244"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="244"/>
-      <c r="F28" s="244"/>
-    </row>
-    <row r="29" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B29" s="256" t="s">
-        <v>584</v>
-      </c>
-      <c r="C29" s="244"/>
-      <c r="D29" s="244"/>
-      <c r="E29" s="244"/>
-      <c r="F29" s="244"/>
-    </row>
-    <row r="30" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B30" s="256" t="s">
-        <v>585</v>
-      </c>
-      <c r="C30" s="244"/>
-      <c r="D30" s="244"/>
-      <c r="E30" s="244"/>
-      <c r="F30" s="244"/>
-    </row>
-    <row r="31" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B31" s="256" t="s">
-        <v>586</v>
-      </c>
-      <c r="C31" s="244"/>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-    </row>
-    <row r="32" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B32" s="259" t="s">
-        <v>587</v>
-      </c>
-      <c r="C32" s="244"/>
-      <c r="D32" s="244"/>
-      <c r="E32" s="244"/>
-      <c r="F32" s="244"/>
-    </row>
-    <row r="33" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B33" s="257" t="s">
-        <v>588</v>
-      </c>
-      <c r="C33" s="244"/>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-    </row>
-    <row r="34" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B34" s="256" t="s">
-        <v>589</v>
-      </c>
-      <c r="C34" s="244"/>
-      <c r="D34" s="244"/>
-      <c r="E34" s="244"/>
-      <c r="F34" s="244"/>
-    </row>
-    <row r="35" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B35" s="264" t="s">
-        <v>719</v>
-      </c>
-      <c r="C35" s="265"/>
-      <c r="D35" s="265"/>
-      <c r="E35" s="265"/>
-      <c r="F35" s="265"/>
+      <c r="C35" s="264"/>
+      <c r="D35" s="264"/>
+      <c r="E35" s="264"/>
+      <c r="F35" s="264"/>
     </row>
     <row r="36" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B36" s="256" t="s">
+      <c r="B36" s="255" t="s">
         <v>590</v>
       </c>
-      <c r="C36" s="244"/>
-      <c r="D36" s="244"/>
-      <c r="E36" s="244"/>
-      <c r="F36" s="244"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
     </row>
     <row r="37" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="255" t="s">
         <v>591</v>
       </c>
-      <c r="C37" s="244"/>
-      <c r="D37" s="244"/>
-      <c r="E37" s="244"/>
-      <c r="F37" s="244"/>
+      <c r="C37" s="245"/>
+      <c r="D37" s="245"/>
+      <c r="E37" s="245"/>
+      <c r="F37" s="245"/>
     </row>
     <row r="38" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B38" s="256" t="s">
+      <c r="B38" s="255" t="s">
         <v>592</v>
       </c>
-      <c r="C38" s="244"/>
-      <c r="D38" s="244"/>
-      <c r="E38" s="244"/>
-      <c r="F38" s="244"/>
+      <c r="C38" s="245"/>
+      <c r="D38" s="245"/>
+      <c r="E38" s="245"/>
+      <c r="F38" s="245"/>
     </row>
     <row r="39" spans="2:6" ht="6" customHeight="1"/>
     <row r="40" spans="2:6" ht="18" customHeight="1">
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="259" t="s">
         <v>593</v>
       </c>
-      <c r="C40" s="244"/>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
+      <c r="C40" s="245"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
     </row>
     <row r="41" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B41" s="266" t="s">
+      <c r="B41" s="267" t="s">
         <v>594</v>
       </c>
-      <c r="C41" s="244"/>
-      <c r="D41" s="244"/>
-      <c r="E41" s="244"/>
-      <c r="F41" s="244"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="245"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
     </row>
     <row r="42" spans="2:6" ht="3.95" customHeight="1"/>
     <row r="43" spans="2:6" ht="15.95" customHeight="1">
@@ -9491,20 +9497,20 @@
       </c>
     </row>
     <row r="44" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B44" s="261" t="s">
+      <c r="B44" s="265" t="s">
         <v>600</v>
       </c>
-      <c r="C44" s="244"/>
-      <c r="D44" s="244"/>
-      <c r="E44" s="244"/>
-      <c r="F44" s="244"/>
+      <c r="C44" s="245"/>
+      <c r="D44" s="245"/>
+      <c r="E44" s="245"/>
+      <c r="F44" s="245"/>
     </row>
     <row r="45" spans="2:6" ht="14.1" customHeight="1">
       <c r="B45" s="171" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="267" t="s">
-        <v>778</v>
+      <c r="C45" s="196" t="s">
+        <v>776</v>
       </c>
       <c r="D45" s="171" t="s">
         <v>602</v>
@@ -9530,8 +9536,8 @@
       <c r="F46" s="164"/>
     </row>
     <row r="47" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B47" s="267" t="s">
-        <v>774</v>
+      <c r="B47" s="196" t="s">
+        <v>772</v>
       </c>
       <c r="C47" s="171" t="s">
         <v>607</v>
@@ -9590,20 +9596,20 @@
       <c r="F50" s="164"/>
     </row>
     <row r="51" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B51" s="261" t="s">
+      <c r="B51" s="265" t="s">
         <v>618</v>
       </c>
-      <c r="C51" s="244"/>
-      <c r="D51" s="244"/>
-      <c r="E51" s="244"/>
-      <c r="F51" s="244"/>
+      <c r="C51" s="245"/>
+      <c r="D51" s="245"/>
+      <c r="E51" s="245"/>
+      <c r="F51" s="245"/>
     </row>
     <row r="52" spans="2:6" ht="14.1" customHeight="1">
       <c r="B52" s="164" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="173" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D52" s="164" t="s">
         <v>619</v>
@@ -9659,17 +9665,17 @@
       <c r="F55" s="171"/>
     </row>
     <row r="56" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B56" s="261" t="s">
+      <c r="B56" s="265" t="s">
         <v>627</v>
       </c>
-      <c r="C56" s="244"/>
-      <c r="D56" s="244"/>
-      <c r="E56" s="244"/>
-      <c r="F56" s="244"/>
+      <c r="C56" s="245"/>
+      <c r="D56" s="245"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="245"/>
     </row>
     <row r="57" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B57" s="267" t="s">
-        <v>775</v>
+      <c r="B57" s="196" t="s">
+        <v>773</v>
       </c>
       <c r="C57" s="171" t="s">
         <v>628</v>
@@ -9713,13 +9719,13 @@
       <c r="F59" s="171"/>
     </row>
     <row r="60" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B60" s="261" t="s">
+      <c r="B60" s="265" t="s">
         <v>635</v>
       </c>
-      <c r="C60" s="244"/>
-      <c r="D60" s="244"/>
-      <c r="E60" s="244"/>
-      <c r="F60" s="244"/>
+      <c r="C60" s="245"/>
+      <c r="D60" s="245"/>
+      <c r="E60" s="245"/>
+      <c r="F60" s="245"/>
     </row>
     <row r="61" spans="2:6" ht="14.1" customHeight="1">
       <c r="B61" s="171" t="s">
@@ -9752,8 +9758,8 @@
       <c r="F62" s="164"/>
     </row>
     <row r="63" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B63" s="267" t="s">
-        <v>779</v>
+      <c r="B63" s="196" t="s">
+        <v>777</v>
       </c>
       <c r="C63" s="171" t="s">
         <v>640</v>
@@ -9768,7 +9774,7 @@
     </row>
     <row r="64" spans="2:6" ht="14.1" customHeight="1">
       <c r="B64" s="173" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C64" s="164" t="s">
         <v>604</v>
@@ -9782,13 +9788,13 @@
       <c r="F64" s="164"/>
     </row>
     <row r="65" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B65" s="261" t="s">
+      <c r="B65" s="265" t="s">
         <v>643</v>
       </c>
-      <c r="C65" s="244"/>
-      <c r="D65" s="244"/>
-      <c r="E65" s="244"/>
-      <c r="F65" s="244"/>
+      <c r="C65" s="245"/>
+      <c r="D65" s="245"/>
+      <c r="E65" s="245"/>
+      <c r="F65" s="245"/>
     </row>
     <row r="66" spans="2:6" ht="14.1" customHeight="1">
       <c r="B66" s="164" t="s">
@@ -9806,14 +9812,14 @@
       <c r="F66" s="164"/>
     </row>
     <row r="67" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B67" s="171" t="s">
+      <c r="B67" s="196" t="s">
+        <v>779</v>
+      </c>
+      <c r="C67" s="171" t="s">
         <v>647</v>
       </c>
-      <c r="C67" s="171" t="s">
+      <c r="D67" s="171" t="s">
         <v>648</v>
-      </c>
-      <c r="D67" s="171" t="s">
-        <v>649</v>
       </c>
       <c r="E67" s="171" t="s">
         <v>646</v>
@@ -9821,14 +9827,14 @@
       <c r="F67" s="171"/>
     </row>
     <row r="68" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B68" s="164" t="s">
-        <v>104</v>
-      </c>
-      <c r="C68" s="164" t="s">
-        <v>650</v>
+      <c r="B68" s="173" t="s">
+        <v>780</v>
+      </c>
+      <c r="C68" s="173" t="s">
+        <v>781</v>
       </c>
       <c r="D68" s="164" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E68" s="164" t="s">
         <v>603</v>
@@ -9836,23 +9842,23 @@
       <c r="F68" s="164"/>
     </row>
     <row r="69" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B69" s="268" t="s">
-        <v>776</v>
-      </c>
-      <c r="C69" s="244"/>
-      <c r="D69" s="244"/>
-      <c r="E69" s="244"/>
-      <c r="F69" s="244"/>
+      <c r="B69" s="266" t="s">
+        <v>774</v>
+      </c>
+      <c r="C69" s="245"/>
+      <c r="D69" s="245"/>
+      <c r="E69" s="245"/>
+      <c r="F69" s="245"/>
     </row>
     <row r="70" spans="2:6" ht="14.1" customHeight="1">
       <c r="B70" s="164" t="s">
         <v>220</v>
       </c>
       <c r="C70" s="164" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D70" s="164" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E70" s="164" t="s">
         <v>603</v>
@@ -9867,7 +9873,7 @@
         <v>622</v>
       </c>
       <c r="D71" s="171" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E71" s="171" t="s">
         <v>603</v>
@@ -9879,10 +9885,10 @@
         <v>224</v>
       </c>
       <c r="C72" s="164" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E72" s="164" t="s">
         <v>603</v>
@@ -9890,23 +9896,23 @@
       <c r="F72" s="164"/>
     </row>
     <row r="73" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B73" s="261" t="s">
-        <v>657</v>
-      </c>
-      <c r="C73" s="244"/>
-      <c r="D73" s="244"/>
-      <c r="E73" s="244"/>
-      <c r="F73" s="244"/>
+      <c r="B73" s="265" t="s">
+        <v>655</v>
+      </c>
+      <c r="C73" s="245"/>
+      <c r="D73" s="245"/>
+      <c r="E73" s="245"/>
+      <c r="F73" s="245"/>
     </row>
     <row r="74" spans="2:6" ht="14.1" customHeight="1">
       <c r="B74" s="164" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C74" s="164" t="s">
         <v>613</v>
       </c>
       <c r="D74" s="164" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E74" s="164" t="s">
         <v>603</v>
@@ -9915,13 +9921,13 @@
     </row>
     <row r="75" spans="2:6" ht="14.1" customHeight="1">
       <c r="B75" s="171" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C75" s="171" t="s">
         <v>633</v>
       </c>
       <c r="D75" s="171" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E75" s="171" t="s">
         <v>603</v>
@@ -9930,13 +9936,13 @@
     </row>
     <row r="76" spans="2:6" ht="14.1" customHeight="1">
       <c r="B76" s="164" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C76" s="164" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D76" s="164" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E76" s="164" t="s">
         <v>603</v>
@@ -9951,7 +9957,7 @@
         <v>601</v>
       </c>
       <c r="D77" s="171" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E77" s="171" t="s">
         <v>603</v>
@@ -9963,10 +9969,10 @@
         <v>287</v>
       </c>
       <c r="C78" s="164" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D78" s="164" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E78" s="164" t="s">
         <v>603</v>
@@ -9978,10 +9984,10 @@
         <v>284</v>
       </c>
       <c r="C79" s="171" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D79" s="171" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E79" s="171" t="s">
         <v>603</v>
@@ -9990,13 +9996,13 @@
     </row>
     <row r="80" spans="2:6" ht="14.1" customHeight="1">
       <c r="B80" s="164" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C80" s="164" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D80" s="164" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E80" s="164" t="s">
         <v>603</v>
@@ -10005,13 +10011,13 @@
     </row>
     <row r="81" spans="2:6" ht="14.1" customHeight="1">
       <c r="B81" s="171" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C81" s="171" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D81" s="171" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E81" s="171" t="s">
         <v>603</v>
@@ -10023,10 +10029,10 @@
         <v>315</v>
       </c>
       <c r="C82" s="164" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D82" s="164" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E82" s="164" t="s">
         <v>603</v>
@@ -10041,7 +10047,7 @@
         <v>622</v>
       </c>
       <c r="D83" s="171" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E83" s="171" t="s">
         <v>603</v>
@@ -10056,7 +10062,7 @@
         <v>622</v>
       </c>
       <c r="D84" s="164" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E84" s="164" t="s">
         <v>603</v>
@@ -10064,53 +10070,53 @@
       <c r="F84" s="164"/>
     </row>
     <row r="85" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B85" s="261" t="s">
-        <v>676</v>
-      </c>
-      <c r="C85" s="244"/>
-      <c r="D85" s="244"/>
-      <c r="E85" s="244"/>
-      <c r="F85" s="244"/>
+      <c r="B85" s="265" t="s">
+        <v>674</v>
+      </c>
+      <c r="C85" s="245"/>
+      <c r="D85" s="245"/>
+      <c r="E85" s="245"/>
+      <c r="F85" s="245"/>
     </row>
     <row r="86" spans="2:6" ht="27.95" customHeight="1">
       <c r="B86" s="164" t="s">
+        <v>675</v>
+      </c>
+      <c r="C86" s="164" t="s">
+        <v>676</v>
+      </c>
+      <c r="D86" s="164" t="s">
         <v>677</v>
       </c>
-      <c r="C86" s="164" t="s">
+      <c r="E86" s="164" t="s">
         <v>678</v>
-      </c>
-      <c r="D86" s="164" t="s">
-        <v>679</v>
-      </c>
-      <c r="E86" s="164" t="s">
-        <v>680</v>
       </c>
       <c r="F86" s="164"/>
     </row>
     <row r="87" spans="2:6" ht="27.95" customHeight="1">
       <c r="B87" s="171" t="s">
+        <v>679</v>
+      </c>
+      <c r="C87" s="171" t="s">
+        <v>680</v>
+      </c>
+      <c r="D87" s="171" t="s">
         <v>681</v>
       </c>
-      <c r="C87" s="171" t="s">
-        <v>682</v>
-      </c>
-      <c r="D87" s="171" t="s">
-        <v>683</v>
-      </c>
       <c r="E87" s="171" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F87" s="171"/>
     </row>
     <row r="88" spans="2:6" ht="6" customHeight="1"/>
     <row r="89" spans="2:6" ht="18" customHeight="1">
-      <c r="B89" s="254" t="s">
-        <v>684</v>
-      </c>
-      <c r="C89" s="244"/>
-      <c r="D89" s="244"/>
-      <c r="E89" s="244"/>
-      <c r="F89" s="244"/>
+      <c r="B89" s="259" t="s">
+        <v>682</v>
+      </c>
+      <c r="C89" s="245"/>
+      <c r="D89" s="245"/>
+      <c r="E89" s="245"/>
+      <c r="F89" s="245"/>
     </row>
     <row r="90" spans="2:6" ht="3.95" customHeight="1"/>
     <row r="91" spans="2:6" ht="15.95" customHeight="1">
@@ -10118,10 +10124,10 @@
         <v>386</v>
       </c>
       <c r="C91" s="163" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D91" s="163" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E91" s="163" t="s">
         <v>23</v>
@@ -10129,87 +10135,110 @@
     </row>
     <row r="92" spans="2:6" ht="14.1" customHeight="1">
       <c r="B92" s="164" t="s">
+        <v>685</v>
+      </c>
+      <c r="C92" s="164" t="s">
+        <v>686</v>
+      </c>
+      <c r="D92" s="164" t="s">
         <v>687</v>
       </c>
-      <c r="C92" s="164" t="s">
+      <c r="E92" s="164" t="s">
         <v>688</v>
-      </c>
-      <c r="D92" s="164" t="s">
-        <v>689</v>
-      </c>
-      <c r="E92" s="164" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="93" spans="2:6" ht="14.1" customHeight="1">
       <c r="B93" s="171" t="s">
+        <v>689</v>
+      </c>
+      <c r="C93" s="171" t="s">
+        <v>690</v>
+      </c>
+      <c r="D93" s="171" t="s">
         <v>691</v>
-      </c>
-      <c r="C93" s="171" t="s">
-        <v>692</v>
-      </c>
-      <c r="D93" s="171" t="s">
-        <v>693</v>
       </c>
       <c r="E93" s="171"/>
     </row>
     <row r="94" spans="2:6" ht="14.1" customHeight="1">
       <c r="B94" s="164" t="s">
+        <v>692</v>
+      </c>
+      <c r="C94" s="164" t="s">
+        <v>693</v>
+      </c>
+      <c r="D94" s="164" t="s">
         <v>694</v>
       </c>
-      <c r="C94" s="164" t="s">
+      <c r="E94" s="164" t="s">
         <v>695</v>
-      </c>
-      <c r="D94" s="164" t="s">
-        <v>696</v>
-      </c>
-      <c r="E94" s="164" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="95" spans="2:6" ht="14.1" customHeight="1">
       <c r="B95" s="171" t="s">
+        <v>696</v>
+      </c>
+      <c r="C95" s="171" t="s">
+        <v>697</v>
+      </c>
+      <c r="D95" s="171" t="s">
         <v>698</v>
       </c>
-      <c r="C95" s="171" t="s">
-        <v>699</v>
-      </c>
-      <c r="D95" s="171" t="s">
-        <v>700</v>
-      </c>
       <c r="E95" s="171" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="96" spans="2:6" ht="14.1" customHeight="1">
       <c r="B96" s="164" t="s">
+        <v>699</v>
+      </c>
+      <c r="C96" s="164" t="s">
+        <v>700</v>
+      </c>
+      <c r="D96" s="164" t="s">
         <v>701</v>
       </c>
-      <c r="C96" s="164" t="s">
+      <c r="E96" s="164" t="s">
         <v>702</v>
-      </c>
-      <c r="D96" s="164" t="s">
-        <v>703</v>
-      </c>
-      <c r="E96" s="164" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="97" spans="2:5" ht="14.1" customHeight="1">
       <c r="B97" s="171" t="s">
+        <v>703</v>
+      </c>
+      <c r="C97" s="171" t="s">
+        <v>704</v>
+      </c>
+      <c r="D97" s="171" t="s">
         <v>705</v>
-      </c>
-      <c r="C97" s="171" t="s">
-        <v>706</v>
-      </c>
-      <c r="D97" s="171" t="s">
-        <v>707</v>
       </c>
       <c r="E97" s="171"/>
     </row>
     <row r="98" spans="2:5" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B24:F24"/>
@@ -10226,29 +10255,6 @@
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10288,15 +10294,15 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" customHeight="1">
       <c r="B3" s="4"/>
-      <c r="C3" s="207" t="s">
+      <c r="C3" s="205" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="208"/>
-      <c r="I3" s="208"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="206"/>
+      <c r="F3" s="206"/>
+      <c r="G3" s="206"/>
+      <c r="H3" s="206"/>
+      <c r="I3" s="206"/>
       <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10" ht="15.95" customHeight="1">
@@ -10312,15 +10318,15 @@
     </row>
     <row r="5" spans="2:10" ht="31.5" customHeight="1">
       <c r="B5" s="6"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="206"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="206"/>
+      <c r="I5" s="206"/>
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="2:10" ht="15.95" customHeight="1">
@@ -10348,11 +10354,11 @@
       <c r="F7" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="210" t="s">
+      <c r="G7" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="211"/>
-      <c r="I7" s="212"/>
+      <c r="H7" s="209"/>
+      <c r="I7" s="210"/>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="2:10" ht="15.95" customHeight="1">
@@ -10365,11 +10371,11 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="200" t="s">
+      <c r="G8" s="201" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="201"/>
-      <c r="I8" s="202"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="203"/>
       <c r="J8" s="5"/>
     </row>
     <row r="9" spans="2:10" ht="15.95" customHeight="1">
@@ -10382,11 +10388,11 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="200" t="s">
-        <v>724</v>
-      </c>
-      <c r="H9" s="201"/>
-      <c r="I9" s="202"/>
+      <c r="G9" s="201" t="s">
+        <v>722</v>
+      </c>
+      <c r="H9" s="202"/>
+      <c r="I9" s="203"/>
       <c r="J9" s="5"/>
     </row>
     <row r="10" spans="2:10" ht="15.95" customHeight="1">
@@ -10399,11 +10405,11 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="200" t="s">
-        <v>725</v>
-      </c>
-      <c r="H10" s="201"/>
-      <c r="I10" s="202"/>
+      <c r="G10" s="201" t="s">
+        <v>723</v>
+      </c>
+      <c r="H10" s="202"/>
+      <c r="I10" s="203"/>
       <c r="J10" s="5"/>
     </row>
     <row r="11" spans="2:10" ht="15.95" customHeight="1">
@@ -10416,11 +10422,11 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="200" t="s">
-        <v>723</v>
-      </c>
-      <c r="H11" s="201"/>
-      <c r="I11" s="202"/>
+      <c r="G11" s="201" t="s">
+        <v>721</v>
+      </c>
+      <c r="H11" s="202"/>
+      <c r="I11" s="203"/>
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="2:10" ht="15.95" customHeight="1">
@@ -10429,9 +10435,9 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="201"/>
-      <c r="I12" s="202"/>
+      <c r="G12" s="204"/>
+      <c r="H12" s="202"/>
+      <c r="I12" s="203"/>
       <c r="J12" s="5"/>
     </row>
     <row r="13" spans="2:10" ht="15.95" customHeight="1">
@@ -10440,9 +10446,9 @@
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="201"/>
-      <c r="I13" s="202"/>
+      <c r="G13" s="204"/>
+      <c r="H13" s="202"/>
+      <c r="I13" s="203"/>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10" ht="15.95" customHeight="1">
@@ -10451,9 +10457,9 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="201"/>
-      <c r="I14" s="202"/>
+      <c r="G14" s="204"/>
+      <c r="H14" s="202"/>
+      <c r="I14" s="203"/>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="2:10" ht="15.95" customHeight="1">
@@ -10462,9 +10468,9 @@
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="203"/>
-      <c r="H15" s="201"/>
-      <c r="I15" s="202"/>
+      <c r="G15" s="204"/>
+      <c r="H15" s="202"/>
+      <c r="I15" s="203"/>
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="2:10" ht="15.95" customHeight="1">
@@ -10473,9 +10479,9 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="202"/>
+      <c r="G16" s="201"/>
+      <c r="H16" s="202"/>
+      <c r="I16" s="203"/>
       <c r="J16" s="5"/>
     </row>
     <row r="17" spans="2:10" ht="15.95" customHeight="1">
@@ -10484,9 +10490,9 @@
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="202"/>
+      <c r="I17" s="203"/>
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="2:10" ht="15.95" customHeight="1">
@@ -10495,9 +10501,9 @@
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="201"/>
-      <c r="I18" s="202"/>
+      <c r="G18" s="201"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="203"/>
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="2:10" ht="15.95" customHeight="1">
@@ -10506,9 +10512,9 @@
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="201"/>
-      <c r="I19" s="202"/>
+      <c r="G19" s="201"/>
+      <c r="H19" s="202"/>
+      <c r="I19" s="203"/>
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="2:10" ht="15.95" customHeight="1">
@@ -10517,9 +10523,9 @@
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="201"/>
-      <c r="I20" s="202"/>
+      <c r="G20" s="201"/>
+      <c r="H20" s="202"/>
+      <c r="I20" s="203"/>
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="2:10" ht="15.95" customHeight="1">
@@ -10528,9 +10534,9 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="201"/>
-      <c r="I21" s="202"/>
+      <c r="G21" s="201"/>
+      <c r="H21" s="202"/>
+      <c r="I21" s="203"/>
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="2:10" ht="15.95" customHeight="1">
@@ -10539,9 +10545,9 @@
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="202"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="202"/>
+      <c r="I22" s="203"/>
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="2:10" ht="15.95" customHeight="1">
@@ -10550,9 +10556,9 @@
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="202"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="202"/>
+      <c r="I23" s="203"/>
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="2:10" ht="15.95" customHeight="1">
@@ -10561,9 +10567,9 @@
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="202"/>
+      <c r="G24" s="201"/>
+      <c r="H24" s="202"/>
+      <c r="I24" s="203"/>
       <c r="J24" s="5"/>
     </row>
     <row r="25" spans="2:10" ht="15.95" customHeight="1">
@@ -10572,9 +10578,9 @@
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="202"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="202"/>
+      <c r="I25" s="203"/>
       <c r="J25" s="5"/>
     </row>
     <row r="26" spans="2:10" ht="15.95" customHeight="1">
@@ -10583,9 +10589,9 @@
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="202"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="202"/>
+      <c r="I26" s="203"/>
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="2:10" ht="15.95" customHeight="1">
@@ -10594,9 +10600,9 @@
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="202"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="202"/>
+      <c r="I27" s="203"/>
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="2:10" ht="15.95" customHeight="1">
@@ -10605,9 +10611,9 @@
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="202"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="202"/>
+      <c r="I28" s="203"/>
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="2:10" ht="15.95" customHeight="1">
@@ -10616,9 +10622,9 @@
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="202"/>
+      <c r="G29" s="201"/>
+      <c r="H29" s="202"/>
+      <c r="I29" s="203"/>
       <c r="J29" s="5"/>
     </row>
     <row r="30" spans="2:10" ht="15.95" customHeight="1">
@@ -10627,9 +10633,9 @@
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="202"/>
+      <c r="G30" s="201"/>
+      <c r="H30" s="202"/>
+      <c r="I30" s="203"/>
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="2:10" ht="15.95" customHeight="1">
@@ -10638,9 +10644,9 @@
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="203"/>
       <c r="J31" s="5"/>
     </row>
     <row r="32" spans="2:10" ht="15.95" customHeight="1">
@@ -10649,9 +10655,9 @@
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="202"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="202"/>
+      <c r="I32" s="203"/>
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="2:10" ht="15.95" customHeight="1">
@@ -10660,9 +10666,9 @@
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="202"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="202"/>
+      <c r="I33" s="203"/>
       <c r="J33" s="5"/>
     </row>
     <row r="34" spans="2:10" ht="15.95" customHeight="1">
@@ -10671,9 +10677,9 @@
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="202"/>
+      <c r="G34" s="201"/>
+      <c r="H34" s="202"/>
+      <c r="I34" s="203"/>
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="2:10" ht="15.95" customHeight="1">
@@ -10682,9 +10688,9 @@
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="202"/>
+      <c r="G35" s="201"/>
+      <c r="H35" s="202"/>
+      <c r="I35" s="203"/>
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="2:10" ht="15.95" customHeight="1">
@@ -10693,9 +10699,9 @@
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="202"/>
+      <c r="G36" s="201"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="2:10" ht="15.95" customHeight="1">
@@ -10704,9 +10710,9 @@
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="202"/>
+      <c r="G37" s="201"/>
+      <c r="H37" s="202"/>
+      <c r="I37" s="203"/>
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="2:10" ht="15.95" customHeight="1">
@@ -10715,9 +10721,9 @@
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
-      <c r="G38" s="200"/>
-      <c r="H38" s="201"/>
-      <c r="I38" s="202"/>
+      <c r="G38" s="201"/>
+      <c r="H38" s="202"/>
+      <c r="I38" s="203"/>
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="2:10" ht="15.95" customHeight="1">
@@ -10726,9 +10732,9 @@
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
-      <c r="G39" s="200"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="202"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="202"/>
+      <c r="I39" s="203"/>
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:10" ht="15.95" customHeight="1">
@@ -10737,9 +10743,9 @@
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="204"/>
-      <c r="H40" s="205"/>
-      <c r="I40" s="206"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="212"/>
+      <c r="I40" s="213"/>
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10" ht="15.95" customHeight="1">
@@ -10755,6 +10761,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G33:I33"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="C3:I3"/>
@@ -10770,27 +10796,7 @@
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G33:I33"/>
     <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G15:I15"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -10832,7 +10838,7 @@
       <c r="S2" s="150"/>
     </row>
     <row r="3" spans="2:33" s="150" customFormat="1" ht="12" customHeight="1">
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="214" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="24" t="s">
@@ -10863,7 +10869,7 @@
       <c r="T3" s="17"/>
     </row>
     <row r="4" spans="2:33" s="150" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="214"/>
+      <c r="B4" s="215"/>
       <c r="C4" s="18"/>
       <c r="S4" s="19"/>
       <c r="T4" s="17"/>
@@ -11079,11 +11085,11 @@
     </row>
     <row r="13" spans="2:33" ht="12" customHeight="1">
       <c r="C13" s="20"/>
-      <c r="D13" s="231" t="s">
+      <c r="D13" s="232" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="223"/>
-      <c r="F13" s="224"/>
+      <c r="E13" s="224"/>
+      <c r="F13" s="225"/>
       <c r="G13" s="38" t="s">
         <v>19</v>
       </c>
@@ -11096,11 +11102,11 @@
       <c r="J13" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="222" t="s">
+      <c r="K13" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="223"/>
-      <c r="M13" s="224"/>
+      <c r="L13" s="224"/>
+      <c r="M13" s="225"/>
       <c r="N13" s="96"/>
       <c r="P13" s="150"/>
       <c r="Q13" s="150"/>
@@ -11115,11 +11121,11 @@
     </row>
     <row r="14" spans="2:33" ht="12" customHeight="1">
       <c r="C14" s="20"/>
-      <c r="D14" s="215" t="s">
+      <c r="D14" s="216" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="216"/>
-      <c r="F14" s="217"/>
+      <c r="E14" s="217"/>
+      <c r="F14" s="218"/>
       <c r="G14" s="40" t="s">
         <v>25</v>
       </c>
@@ -11132,11 +11138,11 @@
       <c r="J14" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="234" t="s">
+      <c r="K14" s="235" t="s">
         <v>27</v>
       </c>
-      <c r="L14" s="216"/>
-      <c r="M14" s="217"/>
+      <c r="L14" s="217"/>
+      <c r="M14" s="218"/>
       <c r="N14" s="96"/>
       <c r="P14" s="150"/>
       <c r="Q14" s="150"/>
@@ -11151,9 +11157,9 @@
     </row>
     <row r="15" spans="2:33" ht="12" customHeight="1">
       <c r="C15" s="20"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="217"/>
+      <c r="D15" s="219"/>
+      <c r="E15" s="217"/>
+      <c r="F15" s="218"/>
       <c r="G15" s="43" t="s">
         <v>28</v>
       </c>
@@ -11166,9 +11172,9 @@
       <c r="J15" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="235"/>
-      <c r="L15" s="216"/>
-      <c r="M15" s="217"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="217"/>
+      <c r="M15" s="218"/>
       <c r="N15" s="96"/>
       <c r="P15" s="150"/>
       <c r="Q15" s="150"/>
@@ -11178,9 +11184,9 @@
     </row>
     <row r="16" spans="2:33" ht="12" customHeight="1">
       <c r="C16" s="20"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="217"/>
+      <c r="D16" s="219"/>
+      <c r="E16" s="217"/>
+      <c r="F16" s="218"/>
       <c r="G16" s="43" t="s">
         <v>29</v>
       </c>
@@ -11193,9 +11199,9 @@
       <c r="J16" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="235"/>
-      <c r="L16" s="216"/>
-      <c r="M16" s="217"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="217"/>
+      <c r="M16" s="218"/>
       <c r="N16" s="96"/>
       <c r="P16" s="150"/>
       <c r="Q16" s="150"/>
@@ -11205,9 +11211,9 @@
     </row>
     <row r="17" spans="2:33" ht="12" customHeight="1">
       <c r="C17" s="20"/>
-      <c r="D17" s="219"/>
-      <c r="E17" s="220"/>
-      <c r="F17" s="221"/>
+      <c r="D17" s="220"/>
+      <c r="E17" s="221"/>
+      <c r="F17" s="222"/>
       <c r="G17" s="43" t="s">
         <v>30</v>
       </c>
@@ -11220,9 +11226,9 @@
       <c r="J17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="235"/>
-      <c r="L17" s="216"/>
-      <c r="M17" s="217"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="217"/>
+      <c r="M17" s="218"/>
       <c r="N17" s="96"/>
       <c r="P17" s="150"/>
       <c r="Q17" s="150"/>
@@ -11232,11 +11238,11 @@
     </row>
     <row r="18" spans="2:33" ht="12" customHeight="1">
       <c r="C18" s="20"/>
-      <c r="D18" s="225" t="s">
+      <c r="D18" s="226" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="226"/>
-      <c r="F18" s="227"/>
+      <c r="E18" s="227"/>
+      <c r="F18" s="228"/>
       <c r="G18" s="43" t="s">
         <v>25</v>
       </c>
@@ -11249,9 +11255,9 @@
       <c r="J18" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="235"/>
-      <c r="L18" s="216"/>
-      <c r="M18" s="217"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="217"/>
+      <c r="M18" s="218"/>
       <c r="N18" s="96"/>
       <c r="P18" s="150"/>
       <c r="Q18" s="150"/>
@@ -11262,9 +11268,9 @@
     <row r="19" spans="2:33" ht="17.25" customHeight="1">
       <c r="B19" s="150"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="220"/>
-      <c r="F19" s="221"/>
+      <c r="D19" s="220"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="222"/>
       <c r="G19" s="46" t="s">
         <v>28</v>
       </c>
@@ -11277,9 +11283,9 @@
       <c r="J19" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="233"/>
-      <c r="L19" s="220"/>
-      <c r="M19" s="221"/>
+      <c r="K19" s="234"/>
+      <c r="L19" s="221"/>
+      <c r="M19" s="222"/>
       <c r="N19" s="150"/>
       <c r="P19" s="150"/>
       <c r="Q19" s="150"/>
@@ -11290,11 +11296,11 @@
     <row r="20" spans="2:33">
       <c r="B20" s="150"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="228" t="s">
+      <c r="D20" s="229" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="229"/>
-      <c r="F20" s="230"/>
+      <c r="E20" s="230"/>
+      <c r="F20" s="231"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -11307,11 +11313,11 @@
       <c r="J20" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="232" t="s">
+      <c r="K20" s="233" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="229"/>
-      <c r="M20" s="230"/>
+      <c r="L20" s="230"/>
+      <c r="M20" s="231"/>
       <c r="N20" s="150"/>
       <c r="P20" s="150"/>
       <c r="Q20" s="150"/>
@@ -11322,9 +11328,9 @@
     <row r="21" spans="2:33" ht="17.25" customHeight="1">
       <c r="B21" s="150"/>
       <c r="C21" s="20"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="220"/>
-      <c r="F21" s="221"/>
+      <c r="D21" s="220"/>
+      <c r="E21" s="221"/>
+      <c r="F21" s="222"/>
       <c r="G21" s="51" t="s">
         <v>28</v>
       </c>
@@ -11337,9 +11343,9 @@
       <c r="J21" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="K21" s="233"/>
-      <c r="L21" s="220"/>
-      <c r="M21" s="221"/>
+      <c r="K21" s="234"/>
+      <c r="L21" s="221"/>
+      <c r="M21" s="222"/>
       <c r="N21" s="150"/>
       <c r="P21" s="150"/>
       <c r="Q21" s="150"/>
@@ -12222,7 +12228,7 @@
       <c r="S56" s="150"/>
     </row>
     <row r="57" spans="2:32" s="150" customFormat="1" ht="12" customHeight="1">
-      <c r="B57" s="213" t="s">
+      <c r="B57" s="214" t="s">
         <v>52</v>
       </c>
       <c r="C57" s="24"/>
@@ -12251,7 +12257,7 @@
       <c r="T57" s="17"/>
     </row>
     <row r="58" spans="2:32" s="150" customFormat="1" ht="12" customHeight="1">
-      <c r="B58" s="214"/>
+      <c r="B58" s="215"/>
       <c r="C58" s="18"/>
       <c r="S58" s="19"/>
       <c r="T58" s="17"/>
@@ -14013,7 +14019,7 @@
       <c r="A2" s="154"/>
     </row>
     <row r="3" spans="1:33" s="150" customFormat="1" ht="12" customHeight="1">
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="214" t="s">
         <v>136</v>
       </c>
       <c r="C3" s="24"/>
@@ -14043,7 +14049,7 @@
     </row>
     <row r="4" spans="1:33" s="150" customFormat="1" ht="12" customHeight="1">
       <c r="A4" s="154"/>
-      <c r="B4" s="214"/>
+      <c r="B4" s="215"/>
       <c r="C4" s="18"/>
       <c r="S4" s="19"/>
       <c r="T4" s="17"/>
@@ -15331,17 +15337,17 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="236" t="s">
+      <c r="A2" s="237" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="237"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237"/>
-      <c r="I2" s="237"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="92" t="s">
@@ -15605,17 +15611,17 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="236" t="s">
+      <c r="A12" s="237" t="s">
         <v>229</v>
       </c>
-      <c r="B12" s="237"/>
-      <c r="C12" s="237"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="237"/>
-      <c r="F12" s="237"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="237"/>
-      <c r="I12" s="237"/>
+      <c r="B12" s="238"/>
+      <c r="C12" s="238"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="238"/>
+      <c r="G12" s="237"/>
+      <c r="H12" s="238"/>
+      <c r="I12" s="238"/>
     </row>
     <row r="13" spans="1:9" ht="16.5" customHeight="1">
       <c r="A13" s="92" t="s">
@@ -15676,17 +15682,17 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="236" t="s">
+      <c r="A15" s="237" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="237"/>
-      <c r="C15" s="237"/>
-      <c r="D15" s="236"/>
-      <c r="E15" s="237"/>
-      <c r="F15" s="237"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="237"/>
-      <c r="I15" s="237"/>
+      <c r="B15" s="238"/>
+      <c r="C15" s="238"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="238"/>
+      <c r="F15" s="238"/>
+      <c r="G15" s="237"/>
+      <c r="H15" s="238"/>
+      <c r="I15" s="238"/>
     </row>
     <row r="16" spans="1:9" ht="16.5" customHeight="1">
       <c r="A16" s="92" t="s">
@@ -16861,23 +16867,23 @@
         <v>23</v>
       </c>
       <c r="J1" s="107" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L1" s="143"/>
     </row>
     <row r="2" spans="1:12" ht="15.95" hidden="1" customHeight="1">
-      <c r="A2" s="238" t="s">
+      <c r="A2" s="241" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="239"/>
-      <c r="C2" s="239"/>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="242"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
     </row>
     <row r="3" spans="1:12" ht="15" hidden="1" customHeight="1">
       <c r="A3" s="92" t="s">
@@ -17036,17 +17042,17 @@
       <c r="J8" s="92"/>
     </row>
     <row r="9" spans="1:12" ht="15.95" customHeight="1">
-      <c r="A9" s="236" t="s">
+      <c r="A9" s="237" t="s">
         <v>288</v>
       </c>
-      <c r="B9" s="237"/>
-      <c r="C9" s="237"/>
-      <c r="D9" s="240"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="237"/>
-      <c r="I9" s="237"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="238"/>
+      <c r="I9" s="238"/>
       <c r="J9" s="156"/>
     </row>
     <row r="10" spans="1:12" ht="15" hidden="1" customHeight="1">
@@ -17513,17 +17519,17 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A26" s="241" t="s">
+      <c r="A26" s="240" t="s">
         <v>311</v>
       </c>
-      <c r="B26" s="237"/>
-      <c r="C26" s="237"/>
-      <c r="D26" s="240"/>
-      <c r="E26" s="237"/>
-      <c r="F26" s="237"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="237"/>
-      <c r="I26" s="237"/>
+      <c r="B26" s="238"/>
+      <c r="C26" s="238"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="238"/>
+      <c r="F26" s="238"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="238"/>
       <c r="J26" s="156"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1">
@@ -17821,17 +17827,17 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A38" s="241" t="s">
+      <c r="A38" s="240" t="s">
         <v>324</v>
       </c>
-      <c r="B38" s="237"/>
-      <c r="C38" s="237"/>
-      <c r="D38" s="240"/>
-      <c r="E38" s="237"/>
-      <c r="F38" s="237"/>
-      <c r="G38" s="240"/>
-      <c r="H38" s="237"/>
-      <c r="I38" s="237"/>
+      <c r="B38" s="238"/>
+      <c r="C38" s="238"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="238"/>
+      <c r="F38" s="238"/>
+      <c r="G38" s="239"/>
+      <c r="H38" s="238"/>
+      <c r="I38" s="238"/>
       <c r="J38" s="156"/>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1">
@@ -18117,17 +18123,17 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A49" s="241" t="s">
+      <c r="A49" s="240" t="s">
         <v>332</v>
       </c>
-      <c r="B49" s="237"/>
-      <c r="C49" s="237"/>
-      <c r="D49" s="240"/>
-      <c r="E49" s="237"/>
-      <c r="F49" s="237"/>
-      <c r="G49" s="240"/>
-      <c r="H49" s="237"/>
-      <c r="I49" s="237"/>
+      <c r="B49" s="238"/>
+      <c r="C49" s="238"/>
+      <c r="D49" s="239"/>
+      <c r="E49" s="238"/>
+      <c r="F49" s="238"/>
+      <c r="G49" s="239"/>
+      <c r="H49" s="238"/>
+      <c r="I49" s="238"/>
       <c r="J49" s="156"/>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1">
@@ -18189,17 +18195,17 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A52" s="241" t="s">
+      <c r="A52" s="240" t="s">
         <v>335</v>
       </c>
-      <c r="B52" s="237"/>
-      <c r="C52" s="237"/>
-      <c r="D52" s="240"/>
-      <c r="E52" s="237"/>
-      <c r="F52" s="237"/>
-      <c r="G52" s="240"/>
-      <c r="H52" s="237"/>
-      <c r="I52" s="237"/>
+      <c r="B52" s="238"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="239"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="239"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
       <c r="J52" s="156"/>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1">
@@ -18320,17 +18326,17 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A57" s="241" t="s">
+      <c r="A57" s="240" t="s">
         <v>342</v>
       </c>
-      <c r="B57" s="237"/>
-      <c r="C57" s="237"/>
-      <c r="D57" s="240"/>
-      <c r="E57" s="237"/>
-      <c r="F57" s="237"/>
-      <c r="G57" s="240"/>
-      <c r="H57" s="237"/>
-      <c r="I57" s="237"/>
+      <c r="B57" s="238"/>
+      <c r="C57" s="238"/>
+      <c r="D57" s="239"/>
+      <c r="E57" s="238"/>
+      <c r="F57" s="238"/>
+      <c r="G57" s="239"/>
+      <c r="H57" s="238"/>
+      <c r="I57" s="238"/>
       <c r="J57" s="156"/>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1">
@@ -18469,17 +18475,17 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A63" s="241" t="s">
+      <c r="A63" s="240" t="s">
         <v>348</v>
       </c>
-      <c r="B63" s="237"/>
-      <c r="C63" s="237"/>
-      <c r="D63" s="240"/>
-      <c r="E63" s="237"/>
-      <c r="F63" s="237"/>
-      <c r="G63" s="240"/>
-      <c r="H63" s="237"/>
-      <c r="I63" s="237"/>
+      <c r="B63" s="238"/>
+      <c r="C63" s="238"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="238"/>
+      <c r="F63" s="238"/>
+      <c r="G63" s="239"/>
+      <c r="H63" s="238"/>
+      <c r="I63" s="238"/>
       <c r="J63" s="156"/>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1">
@@ -18510,17 +18516,17 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A65" s="241" t="s">
+      <c r="A65" s="240" t="s">
         <v>350</v>
       </c>
-      <c r="B65" s="237"/>
-      <c r="C65" s="237"/>
-      <c r="D65" s="240"/>
-      <c r="E65" s="237"/>
-      <c r="F65" s="237"/>
-      <c r="G65" s="240"/>
-      <c r="H65" s="237"/>
-      <c r="I65" s="237"/>
+      <c r="B65" s="238"/>
+      <c r="C65" s="238"/>
+      <c r="D65" s="239"/>
+      <c r="E65" s="238"/>
+      <c r="F65" s="238"/>
+      <c r="G65" s="239"/>
+      <c r="H65" s="238"/>
+      <c r="I65" s="238"/>
       <c r="J65" s="156"/>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
@@ -18605,17 +18611,17 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A69" s="241" t="s">
+      <c r="A69" s="240" t="s">
         <v>354</v>
       </c>
-      <c r="B69" s="237"/>
-      <c r="C69" s="237"/>
-      <c r="D69" s="240"/>
-      <c r="E69" s="237"/>
-      <c r="F69" s="237"/>
-      <c r="G69" s="240"/>
-      <c r="H69" s="237"/>
-      <c r="I69" s="237"/>
+      <c r="B69" s="238"/>
+      <c r="C69" s="238"/>
+      <c r="D69" s="239"/>
+      <c r="E69" s="238"/>
+      <c r="F69" s="238"/>
+      <c r="G69" s="239"/>
+      <c r="H69" s="238"/>
+      <c r="I69" s="238"/>
       <c r="J69" s="156"/>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1">
@@ -18728,17 +18734,17 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="241" t="s">
+      <c r="A74" s="240" t="s">
         <v>359</v>
       </c>
-      <c r="B74" s="237"/>
-      <c r="C74" s="237"/>
-      <c r="D74" s="240"/>
-      <c r="E74" s="237"/>
-      <c r="F74" s="237"/>
-      <c r="G74" s="240"/>
-      <c r="H74" s="237"/>
-      <c r="I74" s="237"/>
+      <c r="B74" s="238"/>
+      <c r="C74" s="238"/>
+      <c r="D74" s="239"/>
+      <c r="E74" s="238"/>
+      <c r="F74" s="238"/>
+      <c r="G74" s="239"/>
+      <c r="H74" s="238"/>
+      <c r="I74" s="238"/>
       <c r="J74" s="156"/>
     </row>
     <row r="75" spans="1:10">
@@ -18770,6 +18776,21 @@
   </sheetData>
   <autoFilter ref="C1:G75"/>
   <mergeCells count="31">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A52:C52"/>
@@ -18786,21 +18807,6 @@
     <mergeCell ref="G49:I49"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="G74:I74"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A49:C49"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18857,35 +18863,35 @@
         <v>362</v>
       </c>
       <c r="K1" s="107" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A2" s="242" t="s">
+      <c r="A2" s="243" t="s">
         <v>363</v>
       </c>
-      <c r="B2" s="237"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="237"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="238"/>
+      <c r="H2" s="238"/>
       <c r="I2" s="106"/>
       <c r="J2" s="106"/>
       <c r="K2" s="106"/>
     </row>
     <row r="3" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A3" s="240" t="s">
+      <c r="A3" s="239" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="237"/>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
+      <c r="B3" s="238"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="238"/>
+      <c r="H3" s="238"/>
       <c r="I3" s="105"/>
       <c r="J3" s="105"/>
       <c r="K3" s="105"/>
@@ -18922,10 +18928,10 @@
         <v>26</v>
       </c>
       <c r="K4" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M4" s="85" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16.5" customHeight="1">
@@ -18960,10 +18966,10 @@
         <v>26</v>
       </c>
       <c r="K5" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M5" s="158" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16.5" customHeight="1">
@@ -18998,10 +19004,10 @@
         <v>26</v>
       </c>
       <c r="K6" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M6" s="85" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16.5" customHeight="1">
@@ -19036,30 +19042,30 @@
         <v>26</v>
       </c>
       <c r="K7" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M7" s="158" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A8" s="240" t="s">
+      <c r="A8" s="239" t="s">
         <v>370</v>
       </c>
-      <c r="B8" s="237"/>
-      <c r="C8" s="237"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="237"/>
-      <c r="F8" s="237"/>
-      <c r="G8" s="237"/>
-      <c r="H8" s="237"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
+      <c r="D8" s="238"/>
+      <c r="E8" s="238"/>
+      <c r="F8" s="238"/>
+      <c r="G8" s="238"/>
+      <c r="H8" s="238"/>
       <c r="I8" s="105"/>
       <c r="J8" s="105"/>
       <c r="K8" s="105"/>
     </row>
     <row r="9" spans="1:13" ht="16.5" customHeight="1">
       <c r="A9" s="89" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B9" s="65" t="s">
         <v>26</v>
@@ -19089,20 +19095,20 @@
         <v>26</v>
       </c>
       <c r="K9" s="89" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="239" t="s">
         <v>371</v>
       </c>
-      <c r="B10" s="237"/>
-      <c r="C10" s="237"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="237"/>
-      <c r="F10" s="237"/>
-      <c r="G10" s="237"/>
-      <c r="H10" s="237"/>
+      <c r="B10" s="238"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
       <c r="I10" s="105"/>
       <c r="J10" s="105"/>
       <c r="K10" s="105"/>
@@ -19139,7 +19145,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="89" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16.5" customHeight="1">
@@ -19174,20 +19180,20 @@
         <v>26</v>
       </c>
       <c r="K12" s="89" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A13" s="240" t="s">
+      <c r="A13" s="239" t="s">
         <v>372</v>
       </c>
-      <c r="B13" s="237"/>
-      <c r="C13" s="237"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="237"/>
-      <c r="F13" s="237"/>
-      <c r="G13" s="237"/>
-      <c r="H13" s="237"/>
+      <c r="B13" s="238"/>
+      <c r="C13" s="238"/>
+      <c r="D13" s="238"/>
+      <c r="E13" s="238"/>
+      <c r="F13" s="238"/>
+      <c r="G13" s="238"/>
+      <c r="H13" s="238"/>
       <c r="I13" s="105"/>
       <c r="J13" s="105"/>
       <c r="K13" s="105"/>
@@ -19224,7 +19230,7 @@
         <v>33</v>
       </c>
       <c r="K14" s="89" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16.5" customHeight="1">
@@ -19259,20 +19265,20 @@
         <v>33</v>
       </c>
       <c r="K15" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A16" s="240" t="s">
+      <c r="A16" s="239" t="s">
         <v>373</v>
       </c>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
+      <c r="B16" s="238"/>
+      <c r="C16" s="238"/>
+      <c r="D16" s="238"/>
+      <c r="E16" s="238"/>
+      <c r="F16" s="238"/>
+      <c r="G16" s="238"/>
+      <c r="H16" s="238"/>
       <c r="I16" s="105"/>
       <c r="J16" s="105"/>
       <c r="K16" s="105"/>
@@ -19309,7 +19315,7 @@
         <v>33</v>
       </c>
       <c r="K17" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.5" customHeight="1">
@@ -19344,43 +19350,43 @@
         <v>33</v>
       </c>
       <c r="K18" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A19" s="242" t="s">
+      <c r="A19" s="243" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="237"/>
-      <c r="C19" s="237"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="237"/>
-      <c r="F19" s="237"/>
-      <c r="G19" s="237"/>
-      <c r="H19" s="237"/>
+      <c r="B19" s="238"/>
+      <c r="C19" s="238"/>
+      <c r="D19" s="238"/>
+      <c r="E19" s="238"/>
+      <c r="F19" s="238"/>
+      <c r="G19" s="238"/>
+      <c r="H19" s="238"/>
       <c r="I19" s="106"/>
       <c r="J19" s="106"/>
       <c r="K19" s="106"/>
       <c r="N19" s="144"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A20" s="241" t="s">
+      <c r="A20" s="240" t="s">
         <v>374</v>
       </c>
-      <c r="B20" s="237"/>
-      <c r="C20" s="237"/>
-      <c r="D20" s="237"/>
-      <c r="E20" s="237"/>
-      <c r="F20" s="237"/>
-      <c r="G20" s="237"/>
-      <c r="H20" s="237"/>
+      <c r="B20" s="238"/>
+      <c r="C20" s="238"/>
+      <c r="D20" s="238"/>
+      <c r="E20" s="238"/>
+      <c r="F20" s="238"/>
+      <c r="G20" s="238"/>
+      <c r="H20" s="238"/>
       <c r="I20" s="105"/>
       <c r="J20" s="105"/>
       <c r="K20" s="105"/>
     </row>
     <row r="21" spans="1:14" ht="22.5" customHeight="1">
       <c r="A21" s="89" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B21" s="65" t="s">
         <v>26</v>
@@ -19410,20 +19416,20 @@
         <v>33</v>
       </c>
       <c r="K21" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A22" s="241" t="s">
+      <c r="A22" s="240" t="s">
         <v>279</v>
       </c>
-      <c r="B22" s="237"/>
-      <c r="C22" s="237"/>
-      <c r="D22" s="237"/>
-      <c r="E22" s="237"/>
-      <c r="F22" s="237"/>
-      <c r="G22" s="237"/>
-      <c r="H22" s="237"/>
+      <c r="B22" s="238"/>
+      <c r="C22" s="238"/>
+      <c r="D22" s="238"/>
+      <c r="E22" s="238"/>
+      <c r="F22" s="238"/>
+      <c r="G22" s="238"/>
+      <c r="H22" s="238"/>
       <c r="I22" s="105"/>
       <c r="J22" s="105"/>
       <c r="K22" s="105"/>
@@ -19460,7 +19466,7 @@
         <v>33</v>
       </c>
       <c r="K23" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -19495,7 +19501,7 @@
         <v>33</v>
       </c>
       <c r="K24" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -19530,7 +19536,7 @@
         <v>33</v>
       </c>
       <c r="K25" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -19565,7 +19571,7 @@
         <v>33</v>
       </c>
       <c r="K26" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
@@ -19600,7 +19606,7 @@
         <v>33</v>
       </c>
       <c r="K27" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="16.5" customHeight="1">
@@ -19635,7 +19641,7 @@
         <v>33</v>
       </c>
       <c r="K28" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="16.5" customHeight="1">
@@ -19670,7 +19676,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="16.5" customHeight="1">
@@ -19705,7 +19711,7 @@
         <v>33</v>
       </c>
       <c r="K30" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1">
@@ -19740,7 +19746,7 @@
         <v>33</v>
       </c>
       <c r="K31" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="16.5" customHeight="1">
@@ -19775,7 +19781,7 @@
         <v>33</v>
       </c>
       <c r="K32" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
@@ -19810,7 +19816,7 @@
         <v>33</v>
       </c>
       <c r="K33" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1">
@@ -19845,20 +19851,20 @@
         <v>33</v>
       </c>
       <c r="K34" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A35" s="241" t="s">
+      <c r="A35" s="240" t="s">
         <v>317</v>
       </c>
-      <c r="B35" s="237"/>
-      <c r="C35" s="237"/>
-      <c r="D35" s="237"/>
-      <c r="E35" s="237"/>
-      <c r="F35" s="237"/>
-      <c r="G35" s="237"/>
-      <c r="H35" s="237"/>
+      <c r="B35" s="238"/>
+      <c r="C35" s="238"/>
+      <c r="D35" s="238"/>
+      <c r="E35" s="238"/>
+      <c r="F35" s="238"/>
+      <c r="G35" s="238"/>
+      <c r="H35" s="238"/>
       <c r="I35" s="105"/>
       <c r="J35" s="105"/>
       <c r="K35" s="105"/>
@@ -19895,7 +19901,7 @@
         <v>26</v>
       </c>
       <c r="K36" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="16.5" customHeight="1">
@@ -19930,20 +19936,20 @@
         <v>26</v>
       </c>
       <c r="K37" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="241" t="s">
+      <c r="A38" s="240" t="s">
         <v>324</v>
       </c>
-      <c r="B38" s="237"/>
-      <c r="C38" s="237"/>
-      <c r="D38" s="237"/>
-      <c r="E38" s="237"/>
-      <c r="F38" s="237"/>
-      <c r="G38" s="237"/>
-      <c r="H38" s="237"/>
+      <c r="B38" s="238"/>
+      <c r="C38" s="238"/>
+      <c r="D38" s="238"/>
+      <c r="E38" s="238"/>
+      <c r="F38" s="238"/>
+      <c r="G38" s="238"/>
+      <c r="H38" s="238"/>
       <c r="I38" s="105"/>
       <c r="J38" s="105"/>
       <c r="K38" s="105"/>
@@ -19980,7 +19986,7 @@
         <v>26</v>
       </c>
       <c r="K39" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="16.5" customHeight="1">
@@ -20015,7 +20021,7 @@
         <v>26</v>
       </c>
       <c r="K40" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="16.5" customHeight="1">
@@ -20050,20 +20056,20 @@
         <v>26</v>
       </c>
       <c r="K41" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="241" t="s">
+      <c r="A42" s="240" t="s">
         <v>379</v>
       </c>
-      <c r="B42" s="237"/>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
-      <c r="G42" s="237"/>
-      <c r="H42" s="237"/>
+      <c r="B42" s="238"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
       <c r="I42" s="105"/>
       <c r="J42" s="105"/>
       <c r="K42" s="105"/>
@@ -20100,7 +20106,7 @@
         <v>26</v>
       </c>
       <c r="K43" s="89" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="16.5" customHeight="1">
@@ -20135,20 +20141,20 @@
         <v>26</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A45" s="241" t="s">
+      <c r="A45" s="240" t="s">
         <v>335</v>
       </c>
-      <c r="B45" s="237"/>
-      <c r="C45" s="237"/>
-      <c r="D45" s="237"/>
-      <c r="E45" s="237"/>
-      <c r="F45" s="237"/>
-      <c r="G45" s="237"/>
-      <c r="H45" s="237"/>
+      <c r="B45" s="238"/>
+      <c r="C45" s="238"/>
+      <c r="D45" s="238"/>
+      <c r="E45" s="238"/>
+      <c r="F45" s="238"/>
+      <c r="G45" s="238"/>
+      <c r="H45" s="238"/>
       <c r="I45" s="105"/>
       <c r="J45" s="105"/>
       <c r="K45" s="105"/>
@@ -20185,7 +20191,7 @@
         <v>33</v>
       </c>
       <c r="K46" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="16.5" customHeight="1">
@@ -20220,7 +20226,7 @@
         <v>33</v>
       </c>
       <c r="K47" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="16.5" customHeight="1">
@@ -20255,7 +20261,7 @@
         <v>33</v>
       </c>
       <c r="K48" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="16.5" customHeight="1">
@@ -20290,20 +20296,20 @@
         <v>33</v>
       </c>
       <c r="K49" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A50" s="241" t="s">
+      <c r="A50" s="240" t="s">
         <v>348</v>
       </c>
-      <c r="B50" s="237"/>
-      <c r="C50" s="237"/>
-      <c r="D50" s="237"/>
-      <c r="E50" s="237"/>
-      <c r="F50" s="237"/>
-      <c r="G50" s="237"/>
-      <c r="H50" s="237"/>
+      <c r="B50" s="238"/>
+      <c r="C50" s="238"/>
+      <c r="D50" s="238"/>
+      <c r="E50" s="238"/>
+      <c r="F50" s="238"/>
+      <c r="G50" s="238"/>
+      <c r="H50" s="238"/>
       <c r="I50" s="105"/>
       <c r="J50" s="105"/>
       <c r="K50" s="105"/>
@@ -20340,20 +20346,20 @@
         <v>33</v>
       </c>
       <c r="K51" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A52" s="241" t="s">
+      <c r="A52" s="240" t="s">
         <v>350</v>
       </c>
-      <c r="B52" s="237"/>
-      <c r="C52" s="237"/>
-      <c r="D52" s="237"/>
-      <c r="E52" s="237"/>
-      <c r="F52" s="237"/>
-      <c r="G52" s="237"/>
-      <c r="H52" s="237"/>
+      <c r="B52" s="238"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
       <c r="I52" s="105"/>
       <c r="J52" s="105"/>
       <c r="K52" s="105"/>
@@ -20390,7 +20396,7 @@
         <v>26</v>
       </c>
       <c r="K53" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="16.5" customHeight="1">
@@ -20425,7 +20431,7 @@
         <v>26</v>
       </c>
       <c r="K54" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="16.5" customHeight="1">
@@ -20458,20 +20464,20 @@
         <v>26</v>
       </c>
       <c r="K55" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A56" s="241" t="s">
+      <c r="A56" s="240" t="s">
         <v>354</v>
       </c>
-      <c r="B56" s="237"/>
-      <c r="C56" s="237"/>
-      <c r="D56" s="237"/>
-      <c r="E56" s="237"/>
-      <c r="F56" s="237"/>
-      <c r="G56" s="237"/>
-      <c r="H56" s="237"/>
+      <c r="B56" s="238"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
       <c r="I56" s="105"/>
       <c r="J56" s="105"/>
       <c r="K56" s="105"/>
@@ -20508,7 +20514,7 @@
         <v>26</v>
       </c>
       <c r="K57" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="16.5" customHeight="1">
@@ -20543,7 +20549,7 @@
         <v>26</v>
       </c>
       <c r="K58" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="16.5" customHeight="1">
@@ -20578,20 +20584,20 @@
         <v>26</v>
       </c>
       <c r="K59" s="89" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A60" s="241" t="s">
+      <c r="A60" s="240" t="s">
         <v>384</v>
       </c>
-      <c r="B60" s="237"/>
-      <c r="C60" s="237"/>
-      <c r="D60" s="237"/>
-      <c r="E60" s="237"/>
-      <c r="F60" s="237"/>
-      <c r="G60" s="237"/>
-      <c r="H60" s="237"/>
+      <c r="B60" s="238"/>
+      <c r="C60" s="238"/>
+      <c r="D60" s="238"/>
+      <c r="E60" s="238"/>
+      <c r="F60" s="238"/>
+      <c r="G60" s="238"/>
+      <c r="H60" s="238"/>
       <c r="I60" s="105"/>
       <c r="J60" s="105"/>
       <c r="K60" s="105"/>
@@ -20628,7 +20634,7 @@
         <v>33</v>
       </c>
       <c r="K61" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="16.5" customHeight="1">
@@ -20663,7 +20669,7 @@
         <v>33</v>
       </c>
       <c r="K62" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="16.5" customHeight="1">
@@ -20698,7 +20704,7 @@
         <v>33</v>
       </c>
       <c r="K63" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="16.5" customHeight="1">
@@ -20733,7 +20739,7 @@
         <v>33</v>
       </c>
       <c r="K64" s="89" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="65" spans="8:8" ht="12" customHeight="1">
@@ -20742,6 +20748,13 @@
   </sheetData>
   <autoFilter ref="B1:F1"/>
   <mergeCells count="17">
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A52:H52"/>
@@ -20752,13 +20765,6 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A56:H56"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20783,23 +20789,23 @@
   <sheetData>
     <row r="1" spans="2:6" ht="6" customHeight="1"/>
     <row r="2" spans="2:6" ht="24" customHeight="1">
-      <c r="B2" s="245" t="s">
-        <v>747</v>
-      </c>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
+      <c r="B2" s="246" t="s">
+        <v>745</v>
+      </c>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
     </row>
     <row r="3" spans="2:6" ht="6" customHeight="1"/>
     <row r="4" spans="2:6" ht="18" customHeight="1">
-      <c r="B4" s="243" t="s">
-        <v>746</v>
-      </c>
-      <c r="C4" s="244"/>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
+      <c r="B4" s="244" t="s">
+        <v>744</v>
+      </c>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="185" t="s">
@@ -20809,10 +20815,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="185" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E5" s="185" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>387</v>
@@ -20823,30 +20829,30 @@
         <v>190</v>
       </c>
       <c r="C6" s="187" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D6" s="187" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F6" s="188" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="54">
       <c r="B7" s="189" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C7" s="190" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D7" s="190" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E7" s="190" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F7" s="191" t="s">
         <v>388</v>
@@ -20854,16 +20860,16 @@
     </row>
     <row r="8" spans="2:6" ht="54">
       <c r="B8" s="186" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C8" s="187" t="s">
+        <v>728</v>
+      </c>
+      <c r="D8" s="187" t="s">
+        <v>729</v>
+      </c>
+      <c r="E8" s="187" t="s">
         <v>730</v>
-      </c>
-      <c r="D8" s="187" t="s">
-        <v>731</v>
-      </c>
-      <c r="E8" s="187" t="s">
-        <v>732</v>
       </c>
       <c r="F8" s="192" t="s">
         <v>388</v>
@@ -20871,13 +20877,13 @@
     </row>
     <row r="9" spans="2:6" ht="6" customHeight="1"/>
     <row r="10" spans="2:6" ht="18" customHeight="1">
-      <c r="B10" s="243" t="s">
-        <v>749</v>
-      </c>
-      <c r="C10" s="244"/>
-      <c r="D10" s="244"/>
-      <c r="E10" s="244"/>
-      <c r="F10" s="244"/>
+      <c r="B10" s="244" t="s">
+        <v>747</v>
+      </c>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="185" t="s">
@@ -20887,36 +20893,36 @@
         <v>18</v>
       </c>
       <c r="D11" s="185" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E11" s="185" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F11" s="185" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B12" s="246" t="s">
-        <v>750</v>
-      </c>
-      <c r="C12" s="244"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
+      <c r="B12" s="247" t="s">
+        <v>748</v>
+      </c>
+      <c r="C12" s="245"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="245"/>
+      <c r="F12" s="245"/>
     </row>
     <row r="13" spans="2:6" ht="54">
       <c r="B13" s="186" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C13" s="187" t="s">
         <v>389</v>
       </c>
       <c r="D13" s="187" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E13" s="187" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F13" s="193" t="s">
         <v>390</v>
@@ -20924,16 +20930,16 @@
     </row>
     <row r="14" spans="2:6" ht="54">
       <c r="B14" s="189" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C14" s="190" t="s">
         <v>377</v>
       </c>
       <c r="D14" s="190" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E14" s="190" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F14" s="194" t="s">
         <v>390</v>
@@ -20941,16 +20947,16 @@
     </row>
     <row r="15" spans="2:6" ht="94.5">
       <c r="B15" s="186" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C15" s="187" t="s">
         <v>378</v>
       </c>
       <c r="D15" s="187" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E15" s="187" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>390</v>
@@ -20958,16 +20964,16 @@
     </row>
     <row r="16" spans="2:6" ht="67.5">
       <c r="B16" s="189" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C16" s="190" t="s">
         <v>391</v>
       </c>
       <c r="D16" s="190" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E16" s="190" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F16" s="194" t="s">
         <v>390</v>
@@ -20975,13 +20981,13 @@
     </row>
     <row r="17" spans="2:6" ht="6" customHeight="1"/>
     <row r="18" spans="2:6" ht="18" customHeight="1">
-      <c r="B18" s="243" t="s">
-        <v>739</v>
-      </c>
-      <c r="C18" s="244"/>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
+      <c r="B18" s="244" t="s">
+        <v>737</v>
+      </c>
+      <c r="C18" s="245"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="185" t="s">
@@ -20991,10 +20997,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="185" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E19" s="185" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F19" s="185" t="s">
         <v>387</v>
@@ -21008,10 +21014,10 @@
         <v>393</v>
       </c>
       <c r="D20" s="187" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E20" s="187" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F20" s="193" t="s">
         <v>390</v>
@@ -21019,13 +21025,13 @@
     </row>
     <row r="21" spans="2:6" ht="6" customHeight="1"/>
     <row r="22" spans="2:6" ht="18" customHeight="1">
-      <c r="B22" s="243" t="s">
-        <v>742</v>
-      </c>
-      <c r="C22" s="244"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
+      <c r="B22" s="244" t="s">
+        <v>740</v>
+      </c>
+      <c r="C22" s="245"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="185" t="s">
@@ -21035,10 +21041,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="185" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E23" s="185" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F23" s="185" t="s">
         <v>387</v>
@@ -21049,13 +21055,13 @@
         <v>394</v>
       </c>
       <c r="C24" s="187" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D24" s="187" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E24" s="187" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F24" s="192" t="s">
         <v>388</v>
@@ -21066,13 +21072,13 @@
         <v>395</v>
       </c>
       <c r="C25" s="190" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D25" s="190" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E25" s="190" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="F25" s="195" t="s">
         <v>396</v>
